--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P963"/>
+  <dimension ref="A1:P961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicenza </t>
+          <t>vicenza</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -16192,7 +16192,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>banca_ditalia</t>
+          <t>piazza_verdi</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -27788,7 +27788,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>ref_00522</t>
+          <t>ref_00523</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -27825,7 +27825,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>ref_00523</t>
+          <t>ref_00522</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -36645,7 +36645,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>interp_00858</t>
+          <t>interp_00860</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -36655,7 +36655,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>marino</t>
+          <t>tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -36665,34 +36665,39 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>marker</t>
+          <t>setting</t>
         </is>
       </c>
       <c r="G859" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>inside</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>interp_00859</t>
+          <t>interp_00861</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>ref_00684</t>
+          <t>ref_00683</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>marino</t>
+          <t>tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -36702,24 +36707,29 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>marker</t>
+          <t>setting</t>
         </is>
       </c>
       <c r="G860" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>inside</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>interp_00860</t>
+          <t>interp_00862</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -36739,7 +36749,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>autista_questura</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
@@ -36761,91 +36771,81 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>interp_00861</t>
+          <t>interp_00863</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>ref_00683</t>
+          <t>ref_00684</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>tenenza_carabinieri_marino</t>
+          <t>via_massimo_dazeglio</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>gaz_marino</t>
+          <t>gaz_via_massimo_dazeglio</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>setting</t>
+          <t>marker</t>
         </is>
       </c>
       <c r="G862" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H862" t="inlineStr">
-        <is>
-          <t>inside</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>interp_00862</t>
+          <t>interp_00864</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>ref_00683</t>
+          <t>ref_00684</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>tenenza_carabinieri_marino</t>
+          <t>via_massimo_dazeglio</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>gaz_marino</t>
+          <t>gaz_via_massimo_dazeglio</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>setting</t>
+          <t>marker</t>
         </is>
       </c>
       <c r="G863" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H863" t="inlineStr">
-        <is>
-          <t>inside</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>interp_00863</t>
+          <t>interp_00865</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -36865,7 +36865,7 @@
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>autista_questura</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
@@ -36882,32 +36882,32 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>interp_00864</t>
+          <t>interp_00866</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>ref_00684</t>
+          <t>ref_00685</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>via_massimo_dazeglio</t>
+          <t>due_santi</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>gaz_via_massimo_dazeglio</t>
+          <t>gaz_due_santi</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>pestalozzi</t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>marker</t>
+          <t>setting</t>
         </is>
       </c>
       <c r="G865" t="inlineStr">
@@ -36919,123 +36919,123 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>interp_00865</t>
+          <t>interp_00867</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>ref_00684</t>
+          <t>ref_00686</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>via_massimo_dazeglio</t>
+          <t>tor_di_gheppio</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>gaz_via_massimo_dazeglio</t>
+          <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>assunta</t>
         </is>
       </c>
       <c r="F866" t="inlineStr">
         <is>
-          <t>marker</t>
+          <t>projectedspace</t>
         </is>
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>interp_00866</t>
+          <t>interp_00868</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>ref_00685</t>
+          <t>ref_00687</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>due_santi</t>
+          <t>via_massimo_dazeglio</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>gaz_due_santi</t>
+          <t>gaz_via_massimo_dazeglio</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>pestalozzi</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
         <is>
-          <t>setting</t>
+          <t>marker</t>
         </is>
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>relative</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>interp_00867</t>
+          <t>interp_00869</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>ref_00686</t>
+          <t>ref_00687</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
+          <t>via_massimo_dazeglio</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>gaz_quarto_di_santa_fumia</t>
+          <t>gaz_via_massimo_dazeglio</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>assunta</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>projectedspace</t>
+          <t>marker</t>
         </is>
       </c>
       <c r="G868" t="inlineStr">
         <is>
           <t>relative</t>
-        </is>
-      </c>
-      <c r="H868" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>interp_00868</t>
+          <t>interp_00870</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -37055,7 +37055,7 @@
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="F869" t="inlineStr">
@@ -37072,7 +37072,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>interp_00869</t>
+          <t>interp_00871</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -37092,7 +37092,7 @@
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="F870" t="inlineStr">
@@ -37109,81 +37109,87 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>interp_00870</t>
+          <t>interp_00872</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>ref_00687</t>
+          <t>ref_00688</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>via_massimo_dazeglio</t>
+          <t>torraccio</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>gaz_via_massimo_dazeglio</t>
+          <t>gaz_torraccio</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>autista_questura</t>
-        </is>
-      </c>
-      <c r="F871" t="inlineStr">
-        <is>
-          <t>marker</t>
-        </is>
-      </c>
-      <c r="G871" t="inlineStr">
-        <is>
-          <t>relative</t>
-        </is>
+          <t>ingravallo</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>routenode</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>tragitto_torraccio_ponte_divino_amore</t>
+        </is>
+      </c>
+      <c r="K871" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>interp_00871</t>
+          <t>interp_00873</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>ref_00687</t>
+          <t>ref_00688</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>via_massimo_dazeglio</t>
+          <t>torraccio</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>gaz_via_massimo_dazeglio</t>
+          <t>gaz_torraccio</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
-        </is>
-      </c>
-      <c r="F872" t="inlineStr">
-        <is>
-          <t>marker</t>
-        </is>
-      </c>
-      <c r="G872" t="inlineStr">
-        <is>
-          <t>relative</t>
-        </is>
+          <t>maresciallo_di_pietrantonio</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>routenode</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>tragitto_torraccio_ponte_divino_amore</t>
+        </is>
+      </c>
+      <c r="K872" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>interp_00872</t>
+          <t>interp_00874</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -37203,7 +37209,7 @@
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -37223,7 +37229,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>interp_00873</t>
+          <t>interp_00875</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -37243,7 +37249,7 @@
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
@@ -37263,27 +37269,27 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>interp_00874</t>
+          <t>interp_00876</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>ref_00688</t>
+          <t>ref_00689</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>torraccio</t>
+          <t>via_appia</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>gaz_torraccio</t>
+          <t>gaz_via_appia</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>autista_questura</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="I875" t="inlineStr">
@@ -37297,33 +37303,33 @@
         </is>
       </c>
       <c r="K875" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>interp_00875</t>
+          <t>interp_00877</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>ref_00688</t>
+          <t>ref_00689</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>torraccio</t>
+          <t>via_appia</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>gaz_torraccio</t>
+          <t>gaz_via_appia</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
@@ -37337,13 +37343,13 @@
         </is>
       </c>
       <c r="K876" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>interp_00876</t>
+          <t>interp_00878</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -37363,7 +37369,7 @@
       </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="I877" t="inlineStr">
@@ -37383,7 +37389,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>interp_00877</t>
+          <t>interp_00879</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -37403,7 +37409,7 @@
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="I878" t="inlineStr">
@@ -37423,27 +37429,27 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>interp_00878</t>
+          <t>interp_00880</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>ref_00689</t>
+          <t>ref_00690</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>via_appia</t>
+          <t>due_santi</t>
         </is>
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>gaz_via_appia</t>
+          <t>gaz_due_santi</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>autista_questura</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
@@ -37457,33 +37463,33 @@
         </is>
       </c>
       <c r="K879" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>interp_00879</t>
+          <t>interp_00881</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>ref_00689</t>
+          <t>ref_00690</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>via_appia</t>
+          <t>due_santi</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>gaz_via_appia</t>
+          <t>gaz_due_santi</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -37497,13 +37503,13 @@
         </is>
       </c>
       <c r="K880" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>interp_00880</t>
+          <t>interp_00882</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -37523,7 +37529,7 @@
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -37543,7 +37549,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>interp_00881</t>
+          <t>interp_00883</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -37563,7 +37569,7 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="I882" t="inlineStr">
@@ -37583,27 +37589,27 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>interp_00882</t>
+          <t>interp_00884</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>ref_00690</t>
+          <t>ref_00691</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>due_santi</t>
+          <t>via_della_falcognana</t>
         </is>
       </c>
       <c r="D883" t="inlineStr">
         <is>
-          <t>gaz_due_santi</t>
+          <t>gaz_via_della_falcognana</t>
         </is>
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t>autista_questura</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
@@ -37617,33 +37623,33 @@
         </is>
       </c>
       <c r="K883" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>interp_00883</t>
+          <t>interp_00885</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>ref_00690</t>
+          <t>ref_00691</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>due_santi</t>
+          <t>via_della_falcognana</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>gaz_due_santi</t>
+          <t>gaz_via_della_falcognana</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
@@ -37657,13 +37663,13 @@
         </is>
       </c>
       <c r="K884" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>interp_00884</t>
+          <t>interp_00886</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -37683,7 +37689,7 @@
       </c>
       <c r="E885" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -37703,7 +37709,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>interp_00885</t>
+          <t>interp_00887</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -37723,7 +37729,7 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -37743,27 +37749,27 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>interp_00886</t>
+          <t>interp_00888</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>ref_00691</t>
+          <t>ref_00692</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>via_della_falcognana</t>
+          <t>via_anziate</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>gaz_via_della_falcognana</t>
+          <t>gaz_via_anziate</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>autista_questura</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">
@@ -37777,33 +37783,33 @@
         </is>
       </c>
       <c r="K887" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>interp_00887</t>
+          <t>interp_00889</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>ref_00691</t>
+          <t>ref_00692</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>via_della_falcognana</t>
+          <t>via_anziate</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>gaz_via_della_falcognana</t>
+          <t>gaz_via_anziate</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -37817,13 +37823,13 @@
         </is>
       </c>
       <c r="K888" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>interp_00888</t>
+          <t>interp_00890</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -37843,7 +37849,7 @@
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -37863,7 +37869,7 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>interp_00889</t>
+          <t>interp_00891</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
@@ -37883,7 +37889,7 @@
       </c>
       <c r="E890" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -37903,27 +37909,32 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>interp_00890</t>
+          <t>interp_00892</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>ref_00692</t>
+          <t>ref_00693</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>via_anziate</t>
+          <t>ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>gaz_via_anziate</t>
+          <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
       <c r="E891" t="inlineStr">
         <is>
-          <t>autista_questura</t>
+          <t>ingravallo</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>inside</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -37937,33 +37948,38 @@
         </is>
       </c>
       <c r="K891" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>interp_00891</t>
+          <t>interp_00893</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>ref_00692</t>
+          <t>ref_00693</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>via_anziate</t>
+          <t>ponte_di_santa_fumia</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
         <is>
-          <t>gaz_via_anziate</t>
+          <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
       <c r="E892" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
+          <t>maresciallo_di_pietrantonio</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>inside</t>
         </is>
       </c>
       <c r="I892" t="inlineStr">
@@ -37977,13 +37993,13 @@
         </is>
       </c>
       <c r="K892" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>interp_00892</t>
+          <t>interp_00894</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -38003,7 +38019,7 @@
       </c>
       <c r="E893" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="H893" t="inlineStr">
@@ -38028,7 +38044,7 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>interp_00893</t>
+          <t>interp_00895</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
@@ -38048,7 +38064,7 @@
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="H894" t="inlineStr">
@@ -38073,17 +38089,17 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>interp_00894</t>
+          <t>interp_00896</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>ref_00693</t>
+          <t>ref_00694</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>ponte_di_santa_fumia</t>
+          <t>tor_di_gheppio</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -38093,12 +38109,12 @@
       </c>
       <c r="E895" t="inlineStr">
         <is>
-          <t>autista_questura</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>near</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
@@ -38112,23 +38128,23 @@
         </is>
       </c>
       <c r="K895" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>interp_00895</t>
+          <t>interp_00897</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>ref_00693</t>
+          <t>ref_00694</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>ponte_di_santa_fumia</t>
+          <t>tor_di_gheppio</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -38138,12 +38154,12 @@
       </c>
       <c r="E896" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t>inside</t>
+          <t>near</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
@@ -38157,13 +38173,13 @@
         </is>
       </c>
       <c r="K896" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>interp_00896</t>
+          <t>interp_00898</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -38183,7 +38199,7 @@
       </c>
       <c r="E897" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="H897" t="inlineStr">
@@ -38208,7 +38224,7 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>interp_00897</t>
+          <t>interp_00899</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
@@ -38228,7 +38244,7 @@
       </c>
       <c r="E898" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="H898" t="inlineStr">
@@ -38253,32 +38269,27 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>interp_00898</t>
+          <t>interp_00900</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>ref_00694</t>
+          <t>ref_00695</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
+          <t>casal_bruciato</t>
         </is>
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>gaz_quarto_di_santa_fumia</t>
+          <t>gaz_casal_bruciato</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
         <is>
-          <t>autista_questura</t>
-        </is>
-      </c>
-      <c r="H899" t="inlineStr">
-        <is>
-          <t>near</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
@@ -38292,38 +38303,33 @@
         </is>
       </c>
       <c r="K899" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>interp_00899</t>
+          <t>interp_00901</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>ref_00694</t>
+          <t>ref_00695</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
+          <t>casal_bruciato</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>gaz_quarto_di_santa_fumia</t>
+          <t>gaz_casal_bruciato</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
-        </is>
-      </c>
-      <c r="H900" t="inlineStr">
-        <is>
-          <t>near</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="I900" t="inlineStr">
@@ -38337,13 +38343,13 @@
         </is>
       </c>
       <c r="K900" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>interp_00900</t>
+          <t>interp_00902</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -38363,7 +38369,7 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
@@ -38383,7 +38389,7 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>interp_00901</t>
+          <t>interp_00903</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
@@ -38403,7 +38409,7 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
@@ -38423,27 +38429,27 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>interp_00902</t>
+          <t>interp_00904</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>ref_00695</t>
+          <t>ref_00696</t>
         </is>
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>casal_bruciato</t>
+          <t>ferrovia_roma_velletri</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_ferrovia_roma_velletri</t>
         </is>
       </c>
       <c r="E903" t="inlineStr">
         <is>
-          <t>autista_questura</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
@@ -38457,33 +38463,33 @@
         </is>
       </c>
       <c r="K903" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>interp_00903</t>
+          <t>interp_00905</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>ref_00695</t>
+          <t>ref_00696</t>
         </is>
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>casal_bruciato</t>
+          <t>ferrovia_roma_velletri</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_ferrovia_roma_velletri</t>
         </is>
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
@@ -38497,13 +38503,13 @@
         </is>
       </c>
       <c r="K904" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>interp_00904</t>
+          <t>interp_00906</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -38523,7 +38529,7 @@
       </c>
       <c r="E905" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
@@ -38543,7 +38549,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>interp_00905</t>
+          <t>interp_00907</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -38563,7 +38569,7 @@
       </c>
       <c r="E906" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
@@ -38583,27 +38589,27 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>interp_00906</t>
+          <t>interp_00908</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>ref_00696</t>
+          <t>ref_00697</t>
         </is>
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>ferrovia_roma_velletri</t>
+          <t>ponte_divino_amore</t>
         </is>
       </c>
       <c r="D907" t="inlineStr">
         <is>
-          <t>gaz_ferrovia_roma_velletri</t>
+          <t>gaz_ponte_divino_amore</t>
         </is>
       </c>
       <c r="E907" t="inlineStr">
         <is>
-          <t>autista_questura</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
@@ -38617,33 +38623,33 @@
         </is>
       </c>
       <c r="K907" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>interp_00907</t>
+          <t>interp_00909</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>ref_00696</t>
+          <t>ref_00697</t>
         </is>
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>ferrovia_roma_velletri</t>
+          <t>ponte_divino_amore</t>
         </is>
       </c>
       <c r="D908" t="inlineStr">
         <is>
-          <t>gaz_ferrovia_roma_velletri</t>
+          <t>gaz_ponte_divino_amore</t>
         </is>
       </c>
       <c r="E908" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
@@ -38657,13 +38663,13 @@
         </is>
       </c>
       <c r="K908" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>interp_00908</t>
+          <t>interp_00910</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
@@ -38683,7 +38689,7 @@
       </c>
       <c r="E909" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -38703,7 +38709,7 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>interp_00909</t>
+          <t>interp_00911</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
@@ -38723,7 +38729,7 @@
       </c>
       <c r="E910" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="I910" t="inlineStr">
@@ -38743,87 +38749,71 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>interp_00910</t>
+          <t>interp_00912</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>ref_00697</t>
+          <t>ref_00698</t>
         </is>
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>ponte_divino_amore</t>
-        </is>
-      </c>
-      <c r="D911" t="inlineStr">
-        <is>
-          <t>gaz_ponte_divino_amore</t>
+          <t>tragitto_torraccio_ponte_divino_amore</t>
         </is>
       </c>
       <c r="E911" t="inlineStr">
         <is>
-          <t>autista_questura</t>
-        </is>
-      </c>
-      <c r="I911" t="inlineStr">
-        <is>
-          <t>routenode</t>
-        </is>
-      </c>
-      <c r="J911" t="inlineStr">
-        <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
-        </is>
-      </c>
-      <c r="K911" t="n">
-        <v>10</v>
+          <t>ingravallo</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>interp_00911</t>
+          <t>interp_00913</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>ref_00697</t>
+          <t>ref_00698</t>
         </is>
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>ponte_divino_amore</t>
-        </is>
-      </c>
-      <c r="D912" t="inlineStr">
-        <is>
-          <t>gaz_ponte_divino_amore</t>
+          <t>tragitto_torraccio_ponte_divino_amore</t>
         </is>
       </c>
       <c r="E912" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
-        </is>
-      </c>
-      <c r="I912" t="inlineStr">
-        <is>
-          <t>routenode</t>
-        </is>
-      </c>
-      <c r="J912" t="inlineStr">
-        <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
-        </is>
-      </c>
-      <c r="K912" t="n">
-        <v>10</v>
+          <t>maresciallo_di_pietrantonio</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>interp_00912</t>
+          <t>interp_00914</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -38838,7 +38828,7 @@
       </c>
       <c r="E913" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>autista_questura</t>
         </is>
       </c>
       <c r="F913" t="inlineStr">
@@ -38855,7 +38845,7 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>interp_00913</t>
+          <t>interp_00915</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -38870,7 +38860,7 @@
       </c>
       <c r="E914" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="F914" t="inlineStr">
@@ -38887,59 +38877,74 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>interp_00914</t>
+          <t>interp_00916</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>ref_00698</t>
+          <t>ref_00699</t>
         </is>
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
+          <t>tor_di_gheppio</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
       <c r="E915" t="inlineStr">
         <is>
-          <t>autista_questura</t>
+          <t>assunta</t>
         </is>
       </c>
       <c r="F915" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>projectedspace</t>
         </is>
       </c>
       <c r="G915" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>interp_00915</t>
+          <t>interp_00917</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>ref_00698</t>
+          <t>ref_00700</t>
         </is>
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
+          <t>palazzo</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>gaz_palazzo</t>
         </is>
       </c>
       <c r="E916" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
+          <t>assunta</t>
         </is>
       </c>
       <c r="F916" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>projectedspace</t>
         </is>
       </c>
       <c r="G916" t="inlineStr">
@@ -38951,74 +38956,69 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>interp_00916</t>
+          <t>interp_00918</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>ref_00699</t>
+          <t>ref_00701</t>
         </is>
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
+          <t>pavona</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
         <is>
-          <t>gaz_quarto_di_santa_fumia</t>
+          <t>gaz_pavona</t>
         </is>
       </c>
       <c r="E917" t="inlineStr">
         <is>
-          <t>assunta</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="F917" t="inlineStr">
         <is>
-          <t>projectedspace</t>
+          <t>marker</t>
         </is>
       </c>
       <c r="G917" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H917" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>interp_00917</t>
+          <t>interp_00919</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>ref_00700</t>
+          <t>ref_00701</t>
         </is>
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>palazzo</t>
+          <t>pavona</t>
         </is>
       </c>
       <c r="D918" t="inlineStr">
         <is>
-          <t>gaz_palazzo</t>
+          <t>gaz_pavona</t>
         </is>
       </c>
       <c r="E918" t="inlineStr">
         <is>
-          <t>assunta</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
         <is>
-          <t>projectedspace</t>
+          <t>marker</t>
         </is>
       </c>
       <c r="G918" t="inlineStr">
@@ -39030,17 +39030,17 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>interp_00918</t>
+          <t>interp_00920</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
         <is>
-          <t>ref_00701</t>
+          <t>ref_00702</t>
         </is>
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>pavona</t>
+          <t>stazione_pavona</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -39061,23 +39061,28 @@
       <c r="G919" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>inside</t>
         </is>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>interp_00919</t>
+          <t>interp_00921</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>ref_00701</t>
+          <t>ref_00702</t>
         </is>
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>pavona</t>
+          <t>stazione_pavona</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -39098,33 +39103,38 @@
       <c r="G920" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>inside</t>
         </is>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>interp_00920</t>
+          <t>interp_00922</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>ref_00702</t>
+          <t>ref_00703</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>stazione_pavona</t>
+          <t>direttissima_roma_napoli</t>
         </is>
       </c>
       <c r="D921" t="inlineStr">
         <is>
-          <t>gaz_pavona</t>
+          <t>gaz_direttissima_roma_napoli</t>
         </is>
       </c>
       <c r="E921" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="F921" t="inlineStr">
@@ -39135,38 +39145,33 @@
       <c r="G921" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H921" t="inlineStr">
-        <is>
-          <t>inside</t>
         </is>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>interp_00921</t>
+          <t>interp_00923</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>ref_00702</t>
+          <t>ref_00703</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>stazione_pavona</t>
+          <t>direttissima_roma_napoli</t>
         </is>
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>gaz_pavona</t>
+          <t>gaz_direttissima_roma_napoli</t>
         </is>
       </c>
       <c r="E922" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>agente_runzato</t>
         </is>
       </c>
       <c r="F922" t="inlineStr">
@@ -39177,33 +39182,28 @@
       <c r="G922" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H922" t="inlineStr">
-        <is>
-          <t>inside</t>
         </is>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>interp_00922</t>
+          <t>interp_00924</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
         <is>
-          <t>ref_00703</t>
+          <t>ref_00704</t>
         </is>
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>direttissima_roma_napoli</t>
+          <t>tor_di_gheppio</t>
         </is>
       </c>
       <c r="D923" t="inlineStr">
         <is>
-          <t>gaz_direttissima_roma_napoli</t>
+          <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
       <c r="E923" t="inlineStr">
@@ -39213,34 +39213,39 @@
       </c>
       <c r="F923" t="inlineStr">
         <is>
-          <t>marker</t>
+          <t>projectedspace</t>
         </is>
       </c>
       <c r="G923" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>interp_00923</t>
+          <t>interp_00925</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>ref_00703</t>
+          <t>ref_00704</t>
         </is>
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>direttissima_roma_napoli</t>
+          <t>tor_di_gheppio</t>
         </is>
       </c>
       <c r="D924" t="inlineStr">
         <is>
-          <t>gaz_direttissima_roma_napoli</t>
+          <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
       <c r="E924" t="inlineStr">
@@ -39250,34 +39255,39 @@
       </c>
       <c r="F924" t="inlineStr">
         <is>
-          <t>marker</t>
+          <t>projectedspace</t>
         </is>
       </c>
       <c r="G924" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>interp_00924</t>
+          <t>interp_00926</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
         <is>
-          <t>ref_00704</t>
+          <t>ref_00705</t>
         </is>
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
+          <t>pavona</t>
         </is>
       </c>
       <c r="D925" t="inlineStr">
         <is>
-          <t>gaz_quarto_di_santa_fumia</t>
+          <t>gaz_pavona</t>
         </is>
       </c>
       <c r="E925" t="inlineStr">
@@ -39293,33 +39303,28 @@
       <c r="G925" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H925" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>interp_00925</t>
+          <t>interp_00927</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>ref_00704</t>
+          <t>ref_00705</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
+          <t>pavona</t>
         </is>
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>gaz_quarto_di_santa_fumia</t>
+          <t>gaz_pavona</t>
         </is>
       </c>
       <c r="E926" t="inlineStr">
@@ -39335,33 +39340,28 @@
       <c r="G926" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H926" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>interp_00926</t>
+          <t>interp_00928</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>ref_00705</t>
+          <t>ref_00706</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>pavona</t>
+          <t>casal_bruciato</t>
         </is>
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>gaz_pavona</t>
+          <t>gaz_casal_bruciato</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -39383,22 +39383,22 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>interp_00927</t>
+          <t>interp_00929</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>ref_00705</t>
+          <t>ref_00706</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>pavona</t>
+          <t>casal_bruciato</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>gaz_pavona</t>
+          <t>gaz_casal_bruciato</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -39420,22 +39420,22 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>interp_00928</t>
+          <t>interp_00930</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
         <is>
-          <t>ref_00706</t>
+          <t>ref_00707</t>
         </is>
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>casal_bruciato</t>
+          <t>via_ardeatina</t>
         </is>
       </c>
       <c r="D929" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_via_ardeatina</t>
         </is>
       </c>
       <c r="E929" t="inlineStr">
@@ -39457,22 +39457,22 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>interp_00929</t>
+          <t>interp_00931</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>ref_00706</t>
+          <t>ref_00707</t>
         </is>
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>casal_bruciato</t>
+          <t>via_ardeatina</t>
         </is>
       </c>
       <c r="D930" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_via_ardeatina</t>
         </is>
       </c>
       <c r="E930" t="inlineStr">
@@ -39494,22 +39494,22 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>interp_00930</t>
+          <t>interp_00932</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
         <is>
-          <t>ref_00707</t>
+          <t>ref_00708</t>
         </is>
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>via_ardeatina</t>
+          <t>ardea</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>gaz_via_ardeatina</t>
+          <t>gaz_ardea</t>
         </is>
       </c>
       <c r="E931" t="inlineStr">
@@ -39531,22 +39531,22 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>interp_00931</t>
+          <t>interp_00933</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>ref_00707</t>
+          <t>ref_00708</t>
         </is>
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>via_ardeatina</t>
+          <t>ardea</t>
         </is>
       </c>
       <c r="D932" t="inlineStr">
         <is>
-          <t>gaz_via_ardeatina</t>
+          <t>gaz_ardea</t>
         </is>
       </c>
       <c r="E932" t="inlineStr">
@@ -39568,22 +39568,22 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>interp_00932</t>
+          <t>interp_00934</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>ref_00708</t>
+          <t>ref_00709</t>
         </is>
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>ardea</t>
+          <t>santa_palomba</t>
         </is>
       </c>
       <c r="D933" t="inlineStr">
         <is>
-          <t>gaz_ardea</t>
+          <t>gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E933" t="inlineStr">
@@ -39605,22 +39605,22 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>interp_00933</t>
+          <t>interp_00935</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>ref_00708</t>
+          <t>ref_00709</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>ardea</t>
+          <t>santa_palomba</t>
         </is>
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>gaz_ardea</t>
+          <t>gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E934" t="inlineStr">
@@ -39642,22 +39642,22 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>interp_00934</t>
+          <t>interp_00936</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>ref_00709</t>
+          <t>ref_00710</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>santa_palomba</t>
+          <t>marino</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>gaz_santa_palomba</t>
+          <t>gaz_marino</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -39679,22 +39679,22 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>interp_00935</t>
+          <t>interp_00937</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>ref_00709</t>
+          <t>ref_00710</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>santa_palomba</t>
+          <t>marino</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>gaz_santa_palomba</t>
+          <t>gaz_marino</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
@@ -39716,22 +39716,22 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>interp_00936</t>
+          <t>interp_00938</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>ref_00710</t>
+          <t>ref_00711</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>marino</t>
+          <t>solforata</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>gaz_marino</t>
+          <t>gaz_solforata</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
@@ -39753,22 +39753,22 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>interp_00937</t>
+          <t>interp_00939</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>ref_00710</t>
+          <t>ref_00711</t>
         </is>
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>marino</t>
+          <t>solforata</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>gaz_marino</t>
+          <t>gaz_solforata</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
@@ -39790,22 +39790,22 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>interp_00938</t>
+          <t>interp_00940</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>ref_00711</t>
+          <t>ref_00712</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>solforata</t>
+          <t>pratica_di_mare</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>gaz_solforata</t>
+          <t>gaz_pratica_di_mare</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -39827,22 +39827,22 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>interp_00939</t>
+          <t>interp_00941</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>ref_00711</t>
+          <t>ref_00712</t>
         </is>
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>solforata</t>
+          <t>pratica_di_mare</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>gaz_solforata</t>
+          <t>gaz_pratica_di_mare</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -39864,22 +39864,22 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>interp_00940</t>
+          <t>interp_00942</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
         <is>
-          <t>ref_00712</t>
+          <t>ref_00713</t>
         </is>
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>pratica_di_mare</t>
+          <t>palazzo</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>gaz_pratica_di_mare</t>
+          <t>gaz_palazzo</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
@@ -39901,22 +39901,22 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>interp_00941</t>
+          <t>interp_00943</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>ref_00712</t>
+          <t>ref_00713</t>
         </is>
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>pratica_di_mare</t>
+          <t>palazzo</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>gaz_pratica_di_mare</t>
+          <t>gaz_palazzo</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -39938,22 +39938,22 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>interp_00942</t>
+          <t>interp_00944</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>ref_00713</t>
+          <t>ref_00714</t>
         </is>
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>palazzo</t>
+          <t>pavona</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>gaz_palazzo</t>
+          <t>gaz_pavona</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
@@ -39975,22 +39975,22 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>interp_00943</t>
+          <t>interp_00945</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>ref_00713</t>
+          <t>ref_00714</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>palazzo</t>
+          <t>pavona</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>gaz_palazzo</t>
+          <t>gaz_pavona</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -40012,22 +40012,22 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>interp_00944</t>
+          <t>interp_00946</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>ref_00714</t>
+          <t>ref_00715</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>pavona</t>
+          <t>casal_bruciato</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>gaz_pavona</t>
+          <t>gaz_casal_bruciato</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -40049,22 +40049,22 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>interp_00945</t>
+          <t>interp_00947</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>ref_00714</t>
+          <t>ref_00715</t>
         </is>
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>pavona</t>
+          <t>casal_bruciato</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>gaz_pavona</t>
+          <t>gaz_casal_bruciato</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
@@ -40086,22 +40086,22 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>interp_00946</t>
+          <t>interp_00948</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>ref_00715</t>
+          <t>ref_00716</t>
         </is>
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>casal_bruciato</t>
+          <t>tor_di_gheppio</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
@@ -40117,28 +40117,33 @@
       <c r="G947" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>interp_00947</t>
+          <t>interp_00949</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>ref_00715</t>
+          <t>ref_00716</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>casal_bruciato</t>
+          <t>tor_di_gheppio</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
@@ -40154,28 +40159,28 @@
       <c r="G948" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>interp_00948</t>
+          <t>interp_00950</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>ref_00716</t>
+          <t>ref_00717</t>
         </is>
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
-        </is>
-      </c>
-      <c r="D949" t="inlineStr">
-        <is>
-          <t>gaz_quarto_di_santa_fumia</t>
+          <t>casa_crocchiapani</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
@@ -40185,39 +40190,29 @@
       </c>
       <c r="F949" t="inlineStr">
         <is>
-          <t>projectedspace</t>
+          <t>setting</t>
         </is>
       </c>
       <c r="G949" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H949" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>interp_00949</t>
+          <t>interp_00951</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>ref_00716</t>
+          <t>ref_00717</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
-        </is>
-      </c>
-      <c r="D950" t="inlineStr">
-        <is>
-          <t>gaz_quarto_di_santa_fumia</t>
+          <t>casa_crocchiapani</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
@@ -40227,24 +40222,19 @@
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t>projectedspace</t>
+          <t>setting</t>
         </is>
       </c>
       <c r="G950" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H950" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>interp_00950</t>
+          <t>interp_00952</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -40259,7 +40249,7 @@
       </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="F951" t="inlineStr">
@@ -40276,7 +40266,7 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>interp_00951</t>
+          <t>interp_00953</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
@@ -40291,7 +40281,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>agente_runzato</t>
+          <t>assunta</t>
         </is>
       </c>
       <c r="F952" t="inlineStr">
@@ -40308,12 +40298,12 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>interp_00952</t>
+          <t>interp_00954</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>ref_00717</t>
+          <t>ref_00718</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
@@ -40323,7 +40313,7 @@
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>assunta</t>
         </is>
       </c>
       <c r="F953" t="inlineStr">
@@ -40333,51 +40323,61 @@
       </c>
       <c r="G953" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>precise</t>
         </is>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>interp_00953</t>
+          <t>interp_00955</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>ref_00717</t>
+          <t>ref_00719</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>casa_crocchiapani</t>
+          <t>tor_di_gheppio</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>assunta</t>
+          <t>veronica_magliarini</t>
         </is>
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t>setting</t>
+          <t>projectedspace</t>
         </is>
       </c>
       <c r="G954" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>interp_00954</t>
+          <t>interp_00956</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>ref_00718</t>
+          <t>ref_00720</t>
         </is>
       </c>
       <c r="C955" t="inlineStr">
@@ -40387,7 +40387,7 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>assunta</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="F955" t="inlineStr">
@@ -40404,49 +40404,39 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>interp_00955</t>
+          <t>interp_00957</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>ref_00719</t>
+          <t>ref_00720</t>
         </is>
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
-        </is>
-      </c>
-      <c r="D956" t="inlineStr">
-        <is>
-          <t>gaz_quarto_di_santa_fumia</t>
+          <t>casa_crocchiapani</t>
         </is>
       </c>
       <c r="E956" t="inlineStr">
         <is>
-          <t>veronica_magliarini</t>
+          <t>maresciallo_di_pietrantonio</t>
         </is>
       </c>
       <c r="F956" t="inlineStr">
         <is>
-          <t>projectedspace</t>
+          <t>setting</t>
         </is>
       </c>
       <c r="G956" t="inlineStr">
         <is>
-          <t>approximate</t>
-        </is>
-      </c>
-      <c r="H956" t="inlineStr">
-        <is>
-          <t>near</t>
+          <t>precise</t>
         </is>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>interp_00956</t>
+          <t>interp_00958</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -40461,7 +40451,7 @@
       </c>
       <c r="E957" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>assunta</t>
         </is>
       </c>
       <c r="F957" t="inlineStr">
@@ -40478,49 +40468,64 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>interp_00957</t>
+          <t>interp_00959</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>ref_00720</t>
+          <t>ref_00721</t>
         </is>
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>casa_crocchiapani</t>
+          <t>tor_di_gheppio</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
       <c r="E958" t="inlineStr">
         <is>
-          <t>maresciallo_di_pietrantonio</t>
+          <t>ingravallo</t>
         </is>
       </c>
       <c r="F958" t="inlineStr">
         <is>
-          <t>setting</t>
+          <t>projectedspace</t>
         </is>
       </c>
       <c r="G958" t="inlineStr">
         <is>
-          <t>precise</t>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>interp_00958</t>
+          <t>interp_00960</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>ref_00720</t>
+          <t>ref_00721</t>
         </is>
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>casa_crocchiapani</t>
+          <t>tor_di_gheppio</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>gaz_quarto_di_santa_fumia</t>
         </is>
       </c>
       <c r="E959" t="inlineStr">
@@ -40530,39 +40535,44 @@
       </c>
       <c r="F959" t="inlineStr">
         <is>
-          <t>setting</t>
+          <t>projectedspace</t>
         </is>
       </c>
       <c r="G959" t="inlineStr">
         <is>
-          <t>precise</t>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>interp_00959</t>
+          <t>interp_00961</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>ref_00721</t>
+          <t>ref_00722</t>
         </is>
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
+          <t>tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="D960" t="inlineStr">
         <is>
-          <t>gaz_quarto_di_santa_fumia</t>
+          <t>gaz_marino</t>
         </is>
       </c>
       <c r="E960" t="inlineStr">
         <is>
-          <t>ingravallo</t>
+          <t>assunta</t>
         </is>
       </c>
       <c r="F960" t="inlineStr">
@@ -40577,34 +40587,34 @@
       </c>
       <c r="H960" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>inside</t>
         </is>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>interp_00960</t>
+          <t>interp_00962</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>ref_00721</t>
+          <t>ref_00722</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>tor_di_gheppio</t>
+          <t>tenenza_carabinieri_marino</t>
         </is>
       </c>
       <c r="D961" t="inlineStr">
         <is>
-          <t>gaz_quarto_di_santa_fumia</t>
+          <t>gaz_marino</t>
         </is>
       </c>
       <c r="E961" t="inlineStr">
         <is>
-          <t>assunta</t>
+          <t>pestalozzi</t>
         </is>
       </c>
       <c r="F961" t="inlineStr">
@@ -40618,90 +40628,6 @@
         </is>
       </c>
       <c r="H961" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-    </row>
-    <row r="962">
-      <c r="A962" t="inlineStr">
-        <is>
-          <t>interp_00961</t>
-        </is>
-      </c>
-      <c r="B962" t="inlineStr">
-        <is>
-          <t>ref_00722</t>
-        </is>
-      </c>
-      <c r="C962" t="inlineStr">
-        <is>
-          <t>tenenza_carabinieri_marino</t>
-        </is>
-      </c>
-      <c r="D962" t="inlineStr">
-        <is>
-          <t>gaz_marino</t>
-        </is>
-      </c>
-      <c r="E962" t="inlineStr">
-        <is>
-          <t>assunta</t>
-        </is>
-      </c>
-      <c r="F962" t="inlineStr">
-        <is>
-          <t>projectedspace</t>
-        </is>
-      </c>
-      <c r="G962" t="inlineStr">
-        <is>
-          <t>relative</t>
-        </is>
-      </c>
-      <c r="H962" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-    </row>
-    <row r="963">
-      <c r="A963" t="inlineStr">
-        <is>
-          <t>interp_00962</t>
-        </is>
-      </c>
-      <c r="B963" t="inlineStr">
-        <is>
-          <t>ref_00722</t>
-        </is>
-      </c>
-      <c r="C963" t="inlineStr">
-        <is>
-          <t>tenenza_carabinieri_marino</t>
-        </is>
-      </c>
-      <c r="D963" t="inlineStr">
-        <is>
-          <t>gaz_marino</t>
-        </is>
-      </c>
-      <c r="E963" t="inlineStr">
-        <is>
-          <t>pestalozzi</t>
-        </is>
-      </c>
-      <c r="F963" t="inlineStr">
-        <is>
-          <t>projectedspace</t>
-        </is>
-      </c>
-      <c r="G963" t="inlineStr">
-        <is>
-          <t>relative</t>
-        </is>
-      </c>
-      <c r="H963" t="inlineStr">
         <is>
           <t>inside</t>
         </is>

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -9073,7 +9073,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>close reading</t>
+          <t>close_reading</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>close reading</t>
+          <t>close_reading</t>
         </is>
       </c>
     </row>
@@ -17131,7 +17131,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaz_brahmaputra </t>
+          <t>gaz_brahmaputra</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaz_brahmaputra </t>
+          <t>gaz_brahmaputra</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -17469,7 +17469,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaz_brahmaputra </t>
+          <t>gaz_brahmaputra</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaz_brahmaputra </t>
+          <t>gaz_brahmaputra</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaz_brahmaputra </t>
+          <t>gaz_brahmaputra</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -23917,7 +23917,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>adjacentTo</t>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -23959,7 +23959,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>adjacentTo</t>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -24869,7 +24869,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>adjacentTo</t>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -24911,7 +24911,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>adjacentTo</t>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>adjacentTo</t>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -26130,7 +26130,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>adjacentTo</t>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -35849,7 +35849,7 @@
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>adjacentTo</t>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -28354,7 +28354,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -28370,6 +28370,16 @@
       <c r="G642" t="inlineStr">
         <is>
           <t>indeterminate</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>near</t>
+        </is>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
         </is>
       </c>
     </row>
@@ -29885,7 +29895,7 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -29901,6 +29911,16 @@
       <c r="G682" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>near</t>
+        </is>
+      </c>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
         </is>
       </c>
     </row>
@@ -30949,7 +30969,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -30965,6 +30985,16 @@
       <c r="G710" t="inlineStr">
         <is>
           <t>precise</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>near</t>
+        </is>
+      </c>
+      <c r="P710" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
         </is>
       </c>
     </row>
@@ -30984,11 +31014,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D711" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E711" t="inlineStr">
         <is>
           <t>pestalozzi</t>
@@ -31002,11 +31027,6 @@
       <c r="G711" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H711" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -31026,11 +31046,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E712" t="inlineStr">
         <is>
           <t>cocullo</t>
@@ -31044,11 +31059,6 @@
       <c r="G712" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H712" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -31137,11 +31147,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D715" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E715" t="inlineStr">
         <is>
           <t>narrator</t>
@@ -31155,11 +31160,6 @@
       <c r="G715" t="inlineStr">
         <is>
           <t>precise</t>
-        </is>
-      </c>
-      <c r="H715" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -31179,11 +31179,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D716" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E716" t="inlineStr">
         <is>
           <t>narrator</t>
@@ -31197,11 +31192,6 @@
       <c r="G716" t="inlineStr">
         <is>
           <t>precise</t>
-        </is>
-      </c>
-      <c r="H716" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -31221,11 +31211,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D717" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E717" t="inlineStr">
         <is>
           <t>nonna_mattonari</t>
@@ -31239,11 +31224,6 @@
       <c r="G717" t="inlineStr">
         <is>
           <t>precise</t>
-        </is>
-      </c>
-      <c r="H717" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -31263,11 +31243,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E718" t="inlineStr">
         <is>
           <t>nonna_mattonari</t>
@@ -31281,11 +31256,6 @@
       <c r="G718" t="inlineStr">
         <is>
           <t>precise</t>
-        </is>
-      </c>
-      <c r="H718" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -31305,11 +31275,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D719" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E719" t="inlineStr">
         <is>
           <t>pestalozzi</t>
@@ -31323,11 +31288,6 @@
       <c r="G719" t="inlineStr">
         <is>
           <t>precise</t>
-        </is>
-      </c>
-      <c r="H719" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -31347,11 +31307,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D720" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E720" t="inlineStr">
         <is>
           <t>cocullo</t>
@@ -31365,11 +31320,6 @@
       <c r="G720" t="inlineStr">
         <is>
           <t>precise</t>
-        </is>
-      </c>
-      <c r="H720" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -31463,11 +31413,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D723" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E723" t="inlineStr">
         <is>
           <t>narrator</t>
@@ -31481,11 +31426,6 @@
       <c r="G723" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H723" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -31658,11 +31598,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D728" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E728" t="inlineStr">
         <is>
           <t>camilla_mattonari</t>
@@ -31676,11 +31611,6 @@
       <c r="G728" t="inlineStr">
         <is>
           <t>precise</t>
-        </is>
-      </c>
-      <c r="H728" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -31700,11 +31630,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D729" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E729" t="inlineStr">
         <is>
           <t>pestalozzi</t>
@@ -31718,11 +31643,6 @@
       <c r="G729" t="inlineStr">
         <is>
           <t>precise</t>
-        </is>
-      </c>
-      <c r="H729" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -31742,11 +31662,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E730" t="inlineStr">
         <is>
           <t>cocullo</t>
@@ -31760,11 +31675,6 @@
       <c r="G730" t="inlineStr">
         <is>
           <t>precise</t>
-        </is>
-      </c>
-      <c r="H730" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -32322,11 +32232,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D745" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E745" t="inlineStr">
         <is>
           <t>camilla_mattonari</t>
@@ -32340,11 +32245,6 @@
       <c r="G745" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H745" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -32448,11 +32348,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D748" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E748" t="inlineStr">
         <is>
           <t>camilla_mattonari</t>
@@ -32466,11 +32361,6 @@
       <c r="G748" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H748" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -32490,11 +32380,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D749" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E749" t="inlineStr">
         <is>
           <t>zio_cantoniere</t>
@@ -32508,11 +32393,6 @@
       <c r="G749" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H749" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -32534,7 +32414,7 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
@@ -32550,6 +32430,16 @@
       <c r="G750" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>near</t>
+        </is>
+      </c>
+      <c r="P750" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
         </is>
       </c>
     </row>
@@ -32969,11 +32859,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D761" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E761" t="inlineStr">
         <is>
           <t>enea_retalli</t>
@@ -32987,11 +32872,6 @@
       <c r="G761" t="inlineStr">
         <is>
           <t>relative</t>
-        </is>
-      </c>
-      <c r="H761" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -33011,11 +32891,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D762" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E762" t="inlineStr">
         <is>
           <t>camilla_mattonari</t>
@@ -33029,11 +32904,6 @@
       <c r="G762" t="inlineStr">
         <is>
           <t>relative</t>
-        </is>
-      </c>
-      <c r="H762" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -33053,11 +32923,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E763" t="inlineStr">
         <is>
           <t>lavinia_mattonari</t>
@@ -33071,11 +32936,6 @@
       <c r="G763" t="inlineStr">
         <is>
           <t>relative</t>
-        </is>
-      </c>
-      <c r="H763" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -33539,11 +33399,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D776" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E776" t="inlineStr">
         <is>
           <t>enea_retalli</t>
@@ -33557,11 +33412,6 @@
       <c r="G776" t="inlineStr">
         <is>
           <t>relative</t>
-        </is>
-      </c>
-      <c r="H776" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -33583,7 +33433,7 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -33599,6 +33449,16 @@
       <c r="G777" t="inlineStr">
         <is>
           <t>relative</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>near</t>
+        </is>
+      </c>
+      <c r="P777" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
         </is>
       </c>
     </row>
@@ -34062,11 +33922,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D790" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E790" t="inlineStr">
         <is>
           <t>enea_retalli</t>
@@ -34080,11 +33935,6 @@
       <c r="G790" t="inlineStr">
         <is>
           <t>relative</t>
-        </is>
-      </c>
-      <c r="H790" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -34104,11 +33954,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D791" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E791" t="inlineStr">
         <is>
           <t>enea_retalli</t>
@@ -34122,11 +33967,6 @@
       <c r="G791" t="inlineStr">
         <is>
           <t>relative</t>
-        </is>
-      </c>
-      <c r="H791" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -34146,11 +33986,6 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
-      <c r="D792" t="inlineStr">
-        <is>
-          <t>gaz_casal_bruciato</t>
-        </is>
-      </c>
       <c r="E792" t="inlineStr">
         <is>
           <t>camilla_mattonari</t>
@@ -34164,11 +33999,6 @@
       <c r="G792" t="inlineStr">
         <is>
           <t>relative</t>
-        </is>
-      </c>
-      <c r="H792" t="inlineStr">
-        <is>
-          <t>near</t>
         </is>
       </c>
     </row>
@@ -38284,12 +38114,17 @@
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
         <is>
           <t>ingravallo</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
@@ -38305,6 +38140,11 @@
       <c r="K899" t="n">
         <v>8</v>
       </c>
+      <c r="P899" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+        </is>
+      </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
@@ -38324,12 +38164,17 @@
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
         <is>
           <t>maresciallo_di_pietrantonio</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
       <c r="I900" t="inlineStr">
@@ -38345,6 +38190,11 @@
       <c r="K900" t="n">
         <v>8</v>
       </c>
+      <c r="P900" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+        </is>
+      </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
@@ -38364,12 +38214,17 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
         <is>
           <t>autista_questura</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
@@ -38385,6 +38240,11 @@
       <c r="K901" t="n">
         <v>8</v>
       </c>
+      <c r="P901" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+        </is>
+      </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
@@ -38404,12 +38264,17 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
         <is>
           <t>agente_runzato</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>near</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
@@ -38425,6 +38290,11 @@
       <c r="K902" t="n">
         <v>8</v>
       </c>
+      <c r="P902" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+        </is>
+      </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
@@ -39361,7 +39231,7 @@
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -39377,6 +39247,16 @@
       <c r="G927" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>near</t>
+        </is>
+      </c>
+      <c r="P927" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
         </is>
       </c>
     </row>
@@ -39398,7 +39278,7 @@
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -39414,6 +39294,16 @@
       <c r="G928" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>near</t>
+        </is>
+      </c>
+      <c r="P928" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
         </is>
       </c>
     </row>
@@ -40027,7 +39917,7 @@
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -40043,6 +39933,16 @@
       <c r="G945" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>near</t>
+        </is>
+      </c>
+      <c r="P945" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
         </is>
       </c>
     </row>
@@ -40064,7 +39964,7 @@
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>gaz_casal_bruciato</t>
+          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
@@ -40080,6 +39980,16 @@
       <c r="G946" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>near</t>
+        </is>
+      </c>
+      <c r="P946" t="inlineStr">
+        <is>
+          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -29076,6 +29076,11 @@
           <t>edicola_due_santi</t>
         </is>
       </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>gaz_edicola_due_santi</t>
+        </is>
+      </c>
       <c r="E661" t="inlineStr">
         <is>
           <t>narrator</t>
@@ -29187,6 +29192,11 @@
           <t>edicola_due_santi</t>
         </is>
       </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>gaz_edicola_due_santi</t>
+        </is>
+      </c>
       <c r="E664" t="inlineStr">
         <is>
           <t>narrator</t>
@@ -29222,6 +29232,11 @@
       <c r="C665" t="inlineStr">
         <is>
           <t>edicola_due_santi</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>gaz_edicola_due_santi</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -28354,7 +28354,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -28372,14 +28372,9 @@
           <t>indeterminate</t>
         </is>
       </c>
-      <c r="H642" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
       <c r="P642" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 212, percorso sognato (Pestalozzi): Manzotti (p. 269) legge «per fil a dest» come un cambio di direzione perpendicolare, in realtà verso sinistra (a sud, verso il Circeo); lettura attribuita, fase 3.</t>
         </is>
       </c>
     </row>
@@ -29910,7 +29905,7 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato|gaz_castel_di_leva|gaz_ponte_divino_amore</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -29935,7 +29930,7 @@
       </c>
       <c r="P682" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
     </row>
@@ -30984,7 +30979,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato|gaz_via_della_falcognana|gaz_ponte_divino_amore|gaz_ferrovia_roma_velletri</t>
         </is>
       </c>
       <c r="E710" t="inlineStr">
@@ -31009,7 +31004,7 @@
       </c>
       <c r="P710" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
     </row>
@@ -31029,6 +31024,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E711" t="inlineStr">
         <is>
           <t>pestalozzi</t>
@@ -31042,6 +31042,11 @@
       <c r="G711" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -31061,6 +31066,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E712" t="inlineStr">
         <is>
           <t>cocullo</t>
@@ -31074,6 +31084,11 @@
       <c r="G712" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -31162,6 +31177,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E715" t="inlineStr">
         <is>
           <t>narrator</t>
@@ -31175,6 +31195,11 @@
       <c r="G715" t="inlineStr">
         <is>
           <t>precise</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -31194,6 +31219,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E716" t="inlineStr">
         <is>
           <t>narrator</t>
@@ -31207,6 +31237,11 @@
       <c r="G716" t="inlineStr">
         <is>
           <t>precise</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -31226,6 +31261,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E717" t="inlineStr">
         <is>
           <t>nonna_mattonari</t>
@@ -31239,6 +31279,11 @@
       <c r="G717" t="inlineStr">
         <is>
           <t>precise</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -31258,6 +31303,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E718" t="inlineStr">
         <is>
           <t>nonna_mattonari</t>
@@ -31271,6 +31321,11 @@
       <c r="G718" t="inlineStr">
         <is>
           <t>precise</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -31290,6 +31345,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E719" t="inlineStr">
         <is>
           <t>pestalozzi</t>
@@ -31303,6 +31363,11 @@
       <c r="G719" t="inlineStr">
         <is>
           <t>precise</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -31322,6 +31387,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E720" t="inlineStr">
         <is>
           <t>cocullo</t>
@@ -31335,6 +31405,11 @@
       <c r="G720" t="inlineStr">
         <is>
           <t>precise</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -31428,6 +31503,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E723" t="inlineStr">
         <is>
           <t>narrator</t>
@@ -31441,6 +31521,11 @@
       <c r="G723" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -31613,6 +31698,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E728" t="inlineStr">
         <is>
           <t>camilla_mattonari</t>
@@ -31626,6 +31716,11 @@
       <c r="G728" t="inlineStr">
         <is>
           <t>precise</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -31645,6 +31740,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E729" t="inlineStr">
         <is>
           <t>pestalozzi</t>
@@ -31658,6 +31758,11 @@
       <c r="G729" t="inlineStr">
         <is>
           <t>precise</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -31677,6 +31782,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E730" t="inlineStr">
         <is>
           <t>cocullo</t>
@@ -31690,6 +31800,11 @@
       <c r="G730" t="inlineStr">
         <is>
           <t>precise</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -32247,6 +32362,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E745" t="inlineStr">
         <is>
           <t>camilla_mattonari</t>
@@ -32260,6 +32380,11 @@
       <c r="G745" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -32363,6 +32488,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E748" t="inlineStr">
         <is>
           <t>camilla_mattonari</t>
@@ -32376,6 +32506,11 @@
       <c r="G748" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -32395,6 +32530,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E749" t="inlineStr">
         <is>
           <t>zio_cantoniere</t>
@@ -32408,6 +32548,11 @@
       <c r="G749" t="inlineStr">
         <is>
           <t>approximate</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -32429,7 +32574,7 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
@@ -32447,14 +32592,9 @@
           <t>approximate</t>
         </is>
       </c>
-      <c r="H750" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
       <c r="P750" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
     </row>
@@ -32874,6 +33014,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E761" t="inlineStr">
         <is>
           <t>enea_retalli</t>
@@ -32887,6 +33032,11 @@
       <c r="G761" t="inlineStr">
         <is>
           <t>relative</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -32906,6 +33056,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E762" t="inlineStr">
         <is>
           <t>camilla_mattonari</t>
@@ -32919,6 +33074,11 @@
       <c r="G762" t="inlineStr">
         <is>
           <t>relative</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -32938,6 +33098,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E763" t="inlineStr">
         <is>
           <t>lavinia_mattonari</t>
@@ -32951,6 +33116,11 @@
       <c r="G763" t="inlineStr">
         <is>
           <t>relative</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -33414,6 +33584,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E776" t="inlineStr">
         <is>
           <t>enea_retalli</t>
@@ -33427,6 +33602,11 @@
       <c r="G776" t="inlineStr">
         <is>
           <t>relative</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -33448,7 +33628,7 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato|gaz_via_ardeatina</t>
         </is>
       </c>
       <c r="E777" t="inlineStr">
@@ -33473,7 +33653,7 @@
       </c>
       <c r="P777" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
     </row>
@@ -33937,6 +34117,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E790" t="inlineStr">
         <is>
           <t>enea_retalli</t>
@@ -33950,6 +34135,11 @@
       <c r="G790" t="inlineStr">
         <is>
           <t>relative</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -33969,6 +34159,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E791" t="inlineStr">
         <is>
           <t>enea_retalli</t>
@@ -33982,6 +34177,11 @@
       <c r="G791" t="inlineStr">
         <is>
           <t>relative</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -34001,6 +34201,11 @@
           <t>casello_km_20_25</t>
         </is>
       </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="E792" t="inlineStr">
         <is>
           <t>camilla_mattonari</t>
@@ -34014,6 +34219,11 @@
       <c r="G792" t="inlineStr">
         <is>
           <t>relative</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
         </is>
       </c>
     </row>
@@ -38129,7 +38339,7 @@
       </c>
       <c r="D899" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato|gaz_ferrovia_roma_velletri</t>
         </is>
       </c>
       <c r="E899" t="inlineStr">
@@ -38157,7 +38367,7 @@
       </c>
       <c r="P899" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
     </row>
@@ -38179,7 +38389,7 @@
       </c>
       <c r="D900" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato|gaz_ferrovia_roma_velletri</t>
         </is>
       </c>
       <c r="E900" t="inlineStr">
@@ -38207,7 +38417,7 @@
       </c>
       <c r="P900" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
     </row>
@@ -38229,7 +38439,7 @@
       </c>
       <c r="D901" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato|gaz_ferrovia_roma_velletri</t>
         </is>
       </c>
       <c r="E901" t="inlineStr">
@@ -38257,7 +38467,7 @@
       </c>
       <c r="P901" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
     </row>
@@ -38279,7 +38489,7 @@
       </c>
       <c r="D902" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato|gaz_ferrovia_roma_velletri</t>
         </is>
       </c>
       <c r="E902" t="inlineStr">
@@ -38307,7 +38517,7 @@
       </c>
       <c r="P902" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
     </row>
@@ -39246,7 +39456,7 @@
       </c>
       <c r="D927" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato|gaz_via_ardeatina|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E927" t="inlineStr">
@@ -39271,7 +39481,7 @@
       </c>
       <c r="P927" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
     </row>
@@ -39293,7 +39503,7 @@
       </c>
       <c r="D928" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato|gaz_via_ardeatina|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E928" t="inlineStr">
@@ -39318,7 +39528,7 @@
       </c>
       <c r="P928" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
     </row>
@@ -39932,7 +40142,7 @@
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato|gaz_via_ardeatina|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -39957,7 +40167,7 @@
       </c>
       <c r="P945" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
     </row>
@@ -39979,7 +40189,7 @@
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>gaz_marino|gaz_albano_laziale|gaz_pavona|gaz_santa_palomba</t>
+          <t>gaz_casale_abbruciato|gaz_via_ardeatina|gaz_santa_palomba</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
@@ -40004,7 +40214,7 @@
       </c>
       <c r="P946" t="inlineStr">
         <is>
-          <t>Ancoraggio relazionale, non un punto: Casal Bruciato è circoscritto a nord/nord-est dai Castelli (Marino, da cui parte Pestalozzi) e dall'Appia verso Albano, a ovest da Pavona, snodo del percorso e della ferrovia, a sud da Santa Palomba e dalle sue antenne. Manzotti (2010, pp. 268–270): il testo e la piantina del Touring collocano Casal Bruciato tra le ferrovie Roma–Velletri e Roma–Napoli, la carta IGM a ovest della Roma–Napoli; la topografia del casello «pare combinare e forse confondere» le due tratte. Il testo stesso attribuisce il nome a una voce popolare: «detto da taluni di Casal Bruciato» (QP 241).</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -9113,6 +9113,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9150,6 +9155,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9187,6 +9197,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9229,6 +9244,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9266,6 +9286,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9303,6 +9328,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9340,6 +9370,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9380,6 +9415,11 @@
       <c r="K153" t="n">
         <v>1</v>
       </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9420,6 +9460,11 @@
       <c r="K154" t="n">
         <v>2</v>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9460,6 +9505,11 @@
       <c r="K155" t="n">
         <v>3</v>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9492,6 +9542,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9529,6 +9584,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9566,6 +9626,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9603,6 +9668,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9640,6 +9710,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9677,6 +9752,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9714,6 +9794,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9751,6 +9836,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9788,6 +9878,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9825,6 +9920,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9862,6 +9962,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9899,6 +10004,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9936,6 +10046,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9973,6 +10088,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10010,6 +10130,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>La visione del sangue produce uno slittamento semantico tra il personaggio di Ingravallo e un elemento biografico centrale dell'esperienza di Gadda, l'esperienza del fronte e la morte del fratello, attraverso il referente topografico del Cengio e del Faiti</t>
@@ -10052,6 +10177,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10089,6 +10219,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10126,6 +10261,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10163,6 +10303,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10200,6 +10345,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10237,6 +10387,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10274,6 +10429,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10311,6 +10471,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10353,6 +10518,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10390,6 +10560,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10427,6 +10602,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10464,6 +10644,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10501,6 +10686,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10543,6 +10733,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10585,6 +10780,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10627,6 +10827,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10669,6 +10874,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10706,6 +10916,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Il monte rappresenta per sineddoche l'origine molisana del protagonista</t>
@@ -10748,6 +10963,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10785,6 +11005,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10822,6 +11047,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10859,6 +11089,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10896,6 +11131,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10933,6 +11173,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10970,6 +11215,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11007,6 +11257,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11044,6 +11299,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11081,6 +11341,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11118,6 +11383,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11155,6 +11425,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11192,6 +11467,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11229,6 +11509,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11266,6 +11551,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11303,6 +11593,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11340,6 +11635,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11429,6 +11729,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11466,6 +11771,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11503,6 +11813,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11540,6 +11855,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11577,6 +11897,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
@@ -11619,6 +11944,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
@@ -11661,6 +11991,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
@@ -11703,6 +12038,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
@@ -11745,6 +12085,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
@@ -11792,6 +12137,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
@@ -11839,6 +12189,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11881,6 +12236,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11918,6 +12278,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11955,6 +12320,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11992,6 +12362,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12029,6 +12404,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12066,6 +12446,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12103,6 +12488,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -12140,6 +12530,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -12177,6 +12572,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12214,6 +12614,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -12251,6 +12656,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12288,6 +12698,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12325,6 +12740,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12362,6 +12782,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12399,6 +12824,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12436,6 +12866,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -12473,6 +12908,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -12510,6 +12950,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -12547,6 +12992,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -12584,6 +13034,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -12626,6 +13081,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -12668,6 +13128,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -12705,6 +13170,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -12742,6 +13212,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -12779,6 +13254,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -12816,6 +13296,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -12853,6 +13338,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -12890,6 +13380,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -12927,6 +13422,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12964,6 +13464,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13001,6 +13506,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13038,6 +13548,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13078,6 +13593,11 @@
       <c r="K250" t="n">
         <v>1</v>
       </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13118,6 +13638,11 @@
       <c r="K251" t="n">
         <v>2</v>
       </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13150,6 +13675,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13187,6 +13717,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13224,6 +13759,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13261,6 +13801,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13298,6 +13843,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -13335,6 +13885,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -13372,6 +13927,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -13409,6 +13969,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -13446,6 +14011,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -13483,6 +14053,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -13520,6 +14095,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -13557,6 +14137,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -13594,6 +14179,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -13631,6 +14221,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -13668,6 +14263,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -13705,6 +14305,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -13742,6 +14347,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13779,6 +14389,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -13821,6 +14436,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -13863,6 +14483,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -13905,6 +14530,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13947,6 +14577,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13984,6 +14619,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14026,6 +14666,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14068,6 +14713,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14105,6 +14755,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14142,6 +14797,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14184,6 +14844,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14335,6 +15000,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="N282" t="inlineStr">
         <is>
           <t>05.05.26</t>
@@ -14377,6 +15047,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14414,6 +15089,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14451,6 +15131,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14488,6 +15173,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14525,6 +15215,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14567,6 +15262,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14604,6 +15304,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -14641,6 +15346,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14678,6 +15388,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -14715,6 +15430,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -14752,6 +15472,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -14789,6 +15514,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -14826,6 +15556,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -14863,6 +15598,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -14900,6 +15640,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -14937,6 +15682,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -14974,6 +15724,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15011,6 +15766,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -15048,6 +15808,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -15085,6 +15850,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -15122,6 +15892,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -15159,6 +15934,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -15196,6 +15976,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -15233,6 +16018,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -15270,6 +16060,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -15307,6 +16102,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -15344,6 +16144,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -15381,6 +16186,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -15418,6 +16228,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -15455,6 +16270,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -15492,6 +16312,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -15529,6 +16354,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -15566,6 +16396,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -15603,6 +16438,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -15640,6 +16480,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -15677,6 +16522,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -15714,6 +16564,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -15751,6 +16606,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -15788,6 +16648,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -15825,6 +16690,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -15862,6 +16732,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -15899,6 +16774,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -15941,6 +16821,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -15983,6 +16868,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -16025,6 +16915,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -16067,6 +16962,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -16104,6 +17004,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -16141,6 +17046,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -16178,6 +17088,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -16215,6 +17130,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -16252,6 +17172,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -16289,6 +17214,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -16326,6 +17256,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -16363,6 +17298,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -16400,6 +17340,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -16437,6 +17382,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -16474,6 +17424,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -16511,6 +17466,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -16548,6 +17508,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -16585,6 +17550,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -16622,6 +17592,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -16659,6 +17634,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -16696,6 +17676,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -16733,6 +17718,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -16770,6 +17760,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -16807,6 +17802,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -16844,6 +17844,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -16881,6 +17886,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -16921,6 +17931,11 @@
       <c r="K351" t="n">
         <v>1</v>
       </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -16961,6 +17976,11 @@
       <c r="K352" t="n">
         <v>2</v>
       </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -17001,6 +18021,11 @@
       <c r="K353" t="n">
         <v>3</v>
       </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -17033,6 +18058,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -17075,6 +18105,11 @@
           <t>0.5</t>
         </is>
       </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -17112,6 +18147,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -17154,6 +18194,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -17191,6 +18236,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -17228,6 +18278,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -17265,6 +18320,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -17302,6 +18362,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -17339,6 +18404,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -17376,6 +18446,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -17413,6 +18488,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -17450,6 +18530,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -17492,6 +18577,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -17534,6 +18624,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -17576,6 +18671,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -17613,6 +18713,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -17650,6 +18755,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -17687,6 +18797,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -17724,6 +18839,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -17761,6 +18881,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -17798,6 +18923,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -17835,6 +18965,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -17872,6 +19007,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -17914,6 +19054,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -17951,6 +19096,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -17988,6 +19138,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -18025,6 +19180,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -18062,6 +19222,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -18099,6 +19264,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -18136,6 +19306,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -18173,6 +19348,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P384" t="inlineStr">
         <is>
           <t>Galilei' = Alessandro Galilei, architetto della facciata di San Giovanni in Laterano. Perifrasi per metonimia dell'autore.</t>
@@ -18215,6 +19395,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -18252,6 +19437,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -18289,6 +19479,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -18326,6 +19521,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -18363,6 +19563,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -18400,6 +19605,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -18437,6 +19647,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -18474,6 +19689,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -18511,6 +19731,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -18548,6 +19773,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -18590,6 +19820,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -18627,6 +19862,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -18664,6 +19904,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -18701,6 +19946,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -18738,6 +19988,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -18775,6 +20030,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -18812,6 +20072,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -18849,6 +20114,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -18886,6 +20156,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -18923,6 +20198,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -18960,6 +20240,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -19000,6 +20285,11 @@
       <c r="K406" t="n">
         <v>1</v>
       </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -19045,6 +20335,11 @@
       <c r="K407" t="n">
         <v>2</v>
       </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -19077,6 +20372,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -19114,6 +20414,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -19151,6 +20456,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -19188,6 +20498,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -19230,6 +20545,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -19710,6 +21030,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -19908,6 +21233,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P426" t="inlineStr">
         <is>
           <t>Area paesaggistica vaga e analogica, delimitata dal Tevere e costruita per accumulo descrittivo (castelli, vigne, colli, monti, piane), contrapposta alla città di Roma; spazio percepito e mitizzato da Liliana Balducci. Il Tevere funziona come barriera idrografica e simbolica di separazione tra spazio urbano e spazio campestre, più che come luogo in sé.</t>
@@ -19950,6 +21280,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P427" t="inlineStr">
         <is>
           <t>Tevere e Biferno sono impiegati come sineddoche spaziale dei tratti diatopici della lingua di Ingravallo</t>
@@ -20096,6 +21431,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -20138,6 +21478,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -20175,6 +21520,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -20212,6 +21562,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -20254,6 +21609,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -20296,6 +21656,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -20338,6 +21703,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -20375,6 +21745,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -20412,6 +21787,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -20449,6 +21829,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -20486,6 +21871,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -20523,6 +21913,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -20560,6 +21955,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -20597,6 +21997,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -20634,6 +22039,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -20671,6 +22081,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -20708,6 +22123,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -20745,6 +22165,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -20782,6 +22207,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -20819,6 +22249,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -20856,6 +22291,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -20893,6 +22333,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -20930,6 +22375,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -20967,6 +22417,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -21004,6 +22459,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -21041,6 +22501,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -21078,6 +22543,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -21115,6 +22585,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -21152,6 +22627,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -21189,6 +22669,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -21226,6 +22711,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -21263,6 +22753,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -21305,6 +22800,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -21342,6 +22842,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -21384,6 +22889,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -21421,6 +22931,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -21458,6 +22973,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -21495,6 +23015,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -21532,6 +23057,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -21574,6 +23104,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -21616,6 +23151,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -21656,6 +23196,11 @@
       <c r="K471" t="n">
         <v>1</v>
       </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -21696,6 +23241,11 @@
       <c r="K472" t="n">
         <v>2</v>
       </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -21746,6 +23296,11 @@
           <t>0.5</t>
         </is>
       </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -21796,6 +23351,11 @@
           <t>0.5</t>
         </is>
       </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -21846,6 +23406,11 @@
           <t>0.5</t>
         </is>
       </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P475" t="inlineStr">
         <is>
           <t>Possibile referente: Castello della Castelluccia, circa 41.7443, 12.6165</t>
@@ -21901,6 +23466,11 @@
           <t>0.5</t>
         </is>
       </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P476" t="inlineStr">
         <is>
           <t>Possibile referente: Castello della Castelluccia, circa 41.7443, 12.6165</t>
@@ -21946,6 +23516,11 @@
       <c r="K477" t="n">
         <v>5</v>
       </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -21978,6 +23553,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -22015,6 +23595,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -22052,6 +23637,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -22089,6 +23679,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -22126,6 +23721,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -22168,6 +23768,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -22208,6 +23813,11 @@
       <c r="K484" t="n">
         <v>1</v>
       </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -22253,6 +23863,11 @@
           <t>0.75</t>
         </is>
       </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -22293,6 +23908,11 @@
       <c r="K486" t="n">
         <v>3</v>
       </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -22333,6 +23953,11 @@
       <c r="K487" t="n">
         <v>4</v>
       </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -22365,6 +23990,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -22407,6 +24037,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -22444,6 +24079,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -22481,6 +24121,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -22521,6 +24166,11 @@
       <c r="K492" t="n">
         <v>1</v>
       </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -22561,6 +24211,11 @@
       <c r="K493" t="n">
         <v>2</v>
       </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -22601,6 +24256,11 @@
       <c r="K494" t="n">
         <v>3</v>
       </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -22641,6 +24301,11 @@
       <c r="K495" t="n">
         <v>4</v>
       </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -22681,6 +24346,11 @@
       <c r="K496" t="n">
         <v>5</v>
       </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -22713,6 +24383,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -22753,6 +24428,11 @@
       <c r="K498" t="n">
         <v>1</v>
       </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -22793,6 +24473,11 @@
       <c r="K499" t="n">
         <v>2</v>
       </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -22833,6 +24518,11 @@
       <c r="K500" t="n">
         <v>3</v>
       </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -22873,6 +24563,11 @@
       <c r="K501" t="n">
         <v>4</v>
       </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -22913,6 +24608,11 @@
       <c r="K502" t="n">
         <v>5</v>
       </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -22945,6 +24645,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -22982,6 +24687,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -23019,6 +24729,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -23061,6 +24776,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -23103,6 +24823,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -23140,6 +24865,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -23177,6 +24907,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -23219,6 +24954,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -23256,6 +24996,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -23293,6 +25038,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -23335,6 +25085,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -23377,6 +25132,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -23414,6 +25174,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -23456,6 +25221,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -23498,6 +25268,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -23535,6 +25310,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -23572,6 +25352,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -23614,6 +25399,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -23656,6 +25446,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -23693,6 +25488,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -23730,6 +25530,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -23767,6 +25572,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -23804,6 +25614,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -23841,6 +25656,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -23878,6 +25698,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -23920,6 +25745,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -23962,6 +25792,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -23999,6 +25834,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -24036,6 +25876,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -24073,6 +25918,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -24110,6 +25960,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -24147,6 +26002,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -24184,6 +26044,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -24221,6 +26086,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -24258,6 +26128,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -24295,6 +26170,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -24335,6 +26215,11 @@
       <c r="K539" t="n">
         <v>1</v>
       </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -24375,6 +26260,11 @@
       <c r="K540" t="n">
         <v>2</v>
       </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -24415,6 +26305,11 @@
       <c r="K541" t="n">
         <v>3</v>
       </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -24455,6 +26350,11 @@
       <c r="K542" t="n">
         <v>4</v>
       </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -24487,6 +26387,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -24524,6 +26429,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -24561,6 +26471,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -24603,6 +26518,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -24645,6 +26565,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -24682,6 +26607,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -24719,6 +26649,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -24756,6 +26691,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -24793,6 +26733,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -24830,6 +26775,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -24872,6 +26822,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -24914,6 +26869,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -24951,6 +26911,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -24993,6 +26958,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -25030,6 +27000,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -25067,6 +27042,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -25104,6 +27084,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -25141,6 +27126,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -25178,6 +27168,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -25215,6 +27210,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -25252,6 +27252,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -25289,6 +27294,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -25326,6 +27336,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -25363,6 +27378,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -25405,6 +27425,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -25447,6 +27472,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -25484,6 +27514,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -25521,6 +27556,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -25558,6 +27598,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -25595,6 +27640,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -25632,6 +27682,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -25669,6 +27724,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -25706,6 +27766,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -25743,6 +27808,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -25780,6 +27850,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -25817,6 +27892,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -25859,6 +27939,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -25896,6 +27981,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -25933,6 +28023,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -25975,6 +28070,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -26012,6 +28112,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -26049,6 +28154,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -26091,6 +28201,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -26133,6 +28248,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -26170,6 +28290,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -26212,6 +28337,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -26249,6 +28379,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -26286,6 +28421,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -26323,6 +28463,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -26360,6 +28505,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -26397,6 +28547,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -26434,6 +28589,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -26471,6 +28631,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -26508,6 +28673,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -26545,6 +28715,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -26587,6 +28762,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -26624,6 +28804,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -26661,6 +28846,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -26698,6 +28888,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -26735,6 +28930,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -26772,6 +28972,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -26817,6 +29022,11 @@
       <c r="K604" t="n">
         <v>1</v>
       </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -26862,6 +29072,11 @@
       <c r="K605" t="n">
         <v>2</v>
       </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -26894,6 +29109,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -26931,6 +29151,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -26968,6 +29193,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -27010,6 +29240,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -27052,6 +29287,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -27089,6 +29329,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -27126,6 +29371,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P612" t="inlineStr">
         <is>
           <t>Giorgio Pinotti identifica esplicitamente la sequenza: «è stata Clelia Farcioni a fare la spia col maresciallo Santarella» nell’incontro di Santa Margherita in Abitacolo. Giorgio Pinotti, “Liliana Balducci e il suo boja?”, (Edinburgh Journal of Gadda Studies)</t>
@@ -27173,6 +29423,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -27215,6 +29470,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -27257,6 +29517,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -27299,6 +29564,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -27341,6 +29611,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -27386,6 +29661,11 @@
       <c r="K618" t="n">
         <v>1</v>
       </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -27431,6 +29711,11 @@
       <c r="K619" t="n">
         <v>1</v>
       </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -27476,6 +29761,11 @@
       <c r="K620" t="n">
         <v>2</v>
       </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -27531,6 +29821,11 @@
       <c r="K621" t="n">
         <v>2</v>
       </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -27581,6 +29876,11 @@
       <c r="K622" t="n">
         <v>3</v>
       </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -27631,6 +29931,11 @@
       <c r="K623" t="n">
         <v>3</v>
       </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -27668,6 +29973,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -27705,6 +30015,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -27742,6 +30057,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -27779,6 +30099,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -27816,6 +30141,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -27853,6 +30183,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -27900,6 +30235,11 @@
           <t>0.7</t>
         </is>
       </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -27937,6 +30277,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -27974,6 +30319,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -28016,6 +30366,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -28058,6 +30413,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -28097,6 +30457,11 @@
       </c>
       <c r="K635" t="n">
         <v>4</v>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
       </c>
       <c r="P635" t="inlineStr">
         <is>
@@ -28145,6 +30510,11 @@
       <c r="K636" t="n">
         <v>4</v>
       </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -28182,6 +30552,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -28224,6 +30599,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -28261,6 +30641,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -28298,6 +30683,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -28335,6 +30725,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -28372,6 +30767,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P642" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 212, percorso sognato (Pestalozzi): Manzotti (p. 269) legge «per fil a dest» come un cambio di direzione perpendicolare, in realtà verso sinistra (a sud, verso il Circeo); lettura attribuita, fase 3.</t>
@@ -28414,6 +30814,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -28451,6 +30856,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -28488,6 +30898,11 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -28530,6 +30945,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -28572,6 +30992,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -28609,6 +31034,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -28646,6 +31076,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -28683,6 +31118,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -28720,6 +31160,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -28760,6 +31205,11 @@
       <c r="K652" t="n">
         <v>5</v>
       </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -28800,6 +31250,11 @@
       <c r="K653" t="n">
         <v>5</v>
       </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -28832,6 +31287,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -28864,6 +31324,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -28901,6 +31366,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -28938,6 +31408,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -28980,6 +31455,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -29017,6 +31497,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -29054,6 +31539,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -29096,6 +31586,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -29133,6 +31628,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -29170,6 +31670,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -29212,6 +31717,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -29254,6 +31764,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -29291,6 +31806,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -29338,6 +31858,11 @@
           <t>0.5</t>
         </is>
       </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -29375,6 +31900,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -29417,6 +31947,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -29459,6 +31994,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -29501,6 +32041,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -29538,6 +32083,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -29575,6 +32125,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -29612,6 +32167,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -29649,6 +32209,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -29691,6 +32256,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -29733,6 +32303,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -29770,6 +32345,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -29812,6 +32392,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -29849,6 +32434,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -29886,6 +32476,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -29928,6 +32523,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P682" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
@@ -29970,6 +32570,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -30007,6 +32612,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -30044,6 +32654,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -30081,6 +32696,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -30118,6 +32738,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -30155,6 +32780,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -30195,6 +32825,11 @@
       <c r="K689" t="n">
         <v>1</v>
       </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -30235,6 +32870,11 @@
       <c r="K690" t="n">
         <v>1</v>
       </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -30275,6 +32915,11 @@
       <c r="K691" t="n">
         <v>1</v>
       </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -30315,6 +32960,11 @@
       <c r="K692" t="n">
         <v>2</v>
       </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -30355,6 +33005,11 @@
       <c r="K693" t="n">
         <v>2</v>
       </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -30395,6 +33050,11 @@
       <c r="K694" t="n">
         <v>2</v>
       </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -30427,6 +33087,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -30459,6 +33124,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -30491,6 +33161,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -30528,6 +33203,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -30570,6 +33250,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -30612,6 +33297,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -30654,6 +33344,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -30696,6 +33391,11 @@
           <t>above</t>
         </is>
       </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -30733,6 +33433,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -30770,6 +33475,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -30807,6 +33517,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -30849,6 +33564,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -30886,6 +33606,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -30923,6 +33648,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -30960,6 +33690,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -31002,6 +33737,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P710" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
@@ -31049,6 +33789,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -31091,6 +33836,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -31123,6 +33873,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -31160,6 +33915,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -31202,6 +33962,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -31244,6 +34009,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -31286,6 +34056,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -31328,6 +34103,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -31370,6 +34150,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -31412,6 +34197,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -31449,6 +34239,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -31486,6 +34281,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -31528,6 +34328,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -31570,6 +34375,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -31607,6 +34417,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -31644,6 +34459,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -31681,6 +34501,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -31723,6 +34548,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -31765,6 +34595,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -31807,6 +34642,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -31844,6 +34684,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -31881,6 +34726,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -31918,6 +34768,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -31955,6 +34810,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -31997,6 +34857,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -32034,6 +34899,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -32071,6 +34941,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -32108,6 +34983,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -32150,6 +35030,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -32192,6 +35077,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -32234,6 +35124,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -32271,6 +35166,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -32308,6 +35208,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -32345,6 +35250,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -32387,6 +35297,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -32429,6 +35344,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -32471,6 +35391,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -32513,6 +35438,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -32555,6 +35485,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -32592,6 +35527,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P750" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
@@ -32634,6 +35574,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -32676,6 +35621,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -32718,6 +35668,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -32760,6 +35715,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -32802,6 +35762,11 @@
           <t>overlaps</t>
         </is>
       </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -32839,6 +35804,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -32881,6 +35851,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -32923,6 +35898,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -32960,6 +35940,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -32997,6 +35982,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -33039,6 +36029,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -33081,6 +36076,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -33123,6 +36123,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -33160,6 +36165,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -33197,6 +36207,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
@@ -33234,6 +36249,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -33271,6 +36291,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -33308,6 +36333,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -33345,6 +36375,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -33382,6 +36417,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -33419,6 +36459,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -33456,6 +36501,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -33493,6 +36543,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -33530,6 +36585,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -33567,6 +36627,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -33609,6 +36674,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -33651,6 +36721,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P777" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
@@ -33693,6 +36768,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -33730,6 +36810,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -33767,6 +36852,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -33804,6 +36894,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -33841,6 +36936,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -33878,6 +36978,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -33915,6 +37020,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -33952,6 +37062,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -33989,6 +37104,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -34026,6 +37146,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -34063,6 +37188,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -34100,6 +37230,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -34142,6 +37277,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -34184,6 +37324,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -34226,6 +37371,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -34263,6 +37413,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -34300,6 +37455,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -34340,6 +37500,11 @@
       <c r="K795" t="n">
         <v>1</v>
       </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -34380,6 +37545,11 @@
       <c r="K796" t="n">
         <v>2</v>
       </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -34412,6 +37582,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -34449,6 +37624,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -34486,6 +37666,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -34528,6 +37713,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -34570,6 +37760,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -34607,6 +37802,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -34644,6 +37844,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -34681,6 +37886,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -34718,6 +37928,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -34755,6 +37970,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -34792,6 +38012,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -34829,6 +38054,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -34866,6 +38096,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -34903,6 +38138,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -34940,6 +38180,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -34977,6 +38222,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -35014,6 +38264,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -35051,6 +38306,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -35088,6 +38348,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -35125,6 +38390,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -35162,6 +38432,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -35199,6 +38474,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -35236,6 +38516,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -35273,6 +38558,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -35310,6 +38600,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -35347,6 +38642,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -35384,6 +38684,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -35421,6 +38726,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -35458,6 +38768,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -35495,6 +38810,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -35532,6 +38852,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -35569,6 +38894,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -35606,6 +38936,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -35643,6 +38978,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -35680,6 +39020,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -35717,6 +39062,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
@@ -35754,6 +39104,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -35791,6 +39146,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -35828,6 +39188,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -35865,6 +39230,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -35907,6 +39277,11 @@
           <t>adjacentto</t>
         </is>
       </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -35944,6 +39319,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -35981,6 +39361,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -36018,6 +39403,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
@@ -36055,6 +39445,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -36092,6 +39487,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -36132,6 +39532,11 @@
       <c r="K843" t="n">
         <v>1</v>
       </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -36172,6 +39577,11 @@
       <c r="K844" t="n">
         <v>1</v>
       </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -36212,6 +39622,11 @@
       <c r="K845" t="n">
         <v>1</v>
       </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -36252,6 +39667,11 @@
       <c r="K846" t="n">
         <v>2</v>
       </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -36292,6 +39712,11 @@
       <c r="K847" t="n">
         <v>2</v>
       </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -36332,6 +39757,11 @@
       <c r="K848" t="n">
         <v>2</v>
       </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -36372,6 +39802,11 @@
       <c r="K849" t="n">
         <v>3</v>
       </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -36412,6 +39847,11 @@
       <c r="K850" t="n">
         <v>3</v>
       </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -36452,6 +39892,11 @@
       <c r="K851" t="n">
         <v>3</v>
       </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -36484,6 +39929,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -36516,6 +39966,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -36548,6 +40003,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -36585,6 +40045,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -36622,6 +40087,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -36659,6 +40129,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -36696,6 +40171,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -36738,6 +40218,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -36780,6 +40265,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -36822,6 +40312,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -36859,6 +40354,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
@@ -36896,6 +40396,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -36933,6 +40438,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -36970,6 +40480,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
@@ -37012,6 +40527,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -37049,6 +40569,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -37086,6 +40611,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
@@ -37123,6 +40653,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -37160,6 +40695,11 @@
           <t>relative</t>
         </is>
       </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -37200,6 +40740,11 @@
       <c r="K871" t="n">
         <v>1</v>
       </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -37240,6 +40785,11 @@
       <c r="K872" t="n">
         <v>1</v>
       </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
@@ -37280,6 +40830,11 @@
       <c r="K873" t="n">
         <v>1</v>
       </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
@@ -37320,6 +40875,11 @@
       <c r="K874" t="n">
         <v>1</v>
       </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
@@ -37360,6 +40920,11 @@
       <c r="K875" t="n">
         <v>2</v>
       </c>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
@@ -37400,6 +40965,11 @@
       <c r="K876" t="n">
         <v>2</v>
       </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
@@ -37440,6 +41010,11 @@
       <c r="K877" t="n">
         <v>2</v>
       </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -37480,6 +41055,11 @@
       <c r="K878" t="n">
         <v>2</v>
       </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -37520,6 +41100,11 @@
       <c r="K879" t="n">
         <v>3</v>
       </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -37560,6 +41145,11 @@
       <c r="K880" t="n">
         <v>3</v>
       </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -37600,6 +41190,11 @@
       <c r="K881" t="n">
         <v>3</v>
       </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -37640,6 +41235,11 @@
       <c r="K882" t="n">
         <v>3</v>
       </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
@@ -37680,6 +41280,11 @@
       <c r="K883" t="n">
         <v>4</v>
       </c>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
@@ -37720,6 +41325,11 @@
       <c r="K884" t="n">
         <v>4</v>
       </c>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
@@ -37760,6 +41370,11 @@
       <c r="K885" t="n">
         <v>4</v>
       </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -37800,6 +41415,11 @@
       <c r="K886" t="n">
         <v>4</v>
       </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -37840,6 +41460,11 @@
       <c r="K887" t="n">
         <v>5</v>
       </c>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
@@ -37880,6 +41505,11 @@
       <c r="K888" t="n">
         <v>5</v>
       </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
@@ -37920,6 +41550,11 @@
       <c r="K889" t="n">
         <v>5</v>
       </c>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
@@ -37960,6 +41595,11 @@
       <c r="K890" t="n">
         <v>5</v>
       </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -38005,6 +41645,11 @@
       <c r="K891" t="n">
         <v>6</v>
       </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -38050,6 +41695,11 @@
       <c r="K892" t="n">
         <v>6</v>
       </c>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
@@ -38095,6 +41745,11 @@
       <c r="K893" t="n">
         <v>6</v>
       </c>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -38140,6 +41795,11 @@
       <c r="K894" t="n">
         <v>6</v>
       </c>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -38185,6 +41845,11 @@
       <c r="K895" t="n">
         <v>7</v>
       </c>
+      <c r="M895" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
@@ -38230,6 +41895,11 @@
       <c r="K896" t="n">
         <v>7</v>
       </c>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
@@ -38275,6 +41945,11 @@
       <c r="K897" t="n">
         <v>7</v>
       </c>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
@@ -38320,6 +41995,11 @@
       <c r="K898" t="n">
         <v>7</v>
       </c>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -38365,6 +42045,11 @@
       <c r="K899" t="n">
         <v>8</v>
       </c>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P899" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
@@ -38415,6 +42100,11 @@
       <c r="K900" t="n">
         <v>8</v>
       </c>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P900" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
@@ -38465,6 +42155,11 @@
       <c r="K901" t="n">
         <v>8</v>
       </c>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P901" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
@@ -38515,6 +42210,11 @@
       <c r="K902" t="n">
         <v>8</v>
       </c>
+      <c r="M902" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P902" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
@@ -38560,6 +42260,11 @@
       <c r="K903" t="n">
         <v>9</v>
       </c>
+      <c r="M903" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
@@ -38600,6 +42305,11 @@
       <c r="K904" t="n">
         <v>9</v>
       </c>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
@@ -38640,6 +42350,11 @@
       <c r="K905" t="n">
         <v>9</v>
       </c>
+      <c r="M905" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
@@ -38680,6 +42395,11 @@
       <c r="K906" t="n">
         <v>9</v>
       </c>
+      <c r="M906" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
@@ -38720,6 +42440,11 @@
       <c r="K907" t="n">
         <v>10</v>
       </c>
+      <c r="M907" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
@@ -38760,6 +42485,11 @@
       <c r="K908" t="n">
         <v>10</v>
       </c>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
@@ -38800,6 +42530,11 @@
       <c r="K909" t="n">
         <v>10</v>
       </c>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -38840,6 +42575,11 @@
       <c r="K910" t="n">
         <v>10</v>
       </c>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
@@ -38872,6 +42612,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -38904,6 +42649,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -38936,6 +42686,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M913" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -38968,6 +42723,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
@@ -39010,6 +42770,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
@@ -39047,6 +42812,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M916" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -39084,6 +42854,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M917" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
@@ -39121,6 +42896,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M918" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
@@ -39163,6 +42943,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M919" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -39205,6 +42990,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -39242,6 +43032,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -39279,6 +43074,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -39321,6 +43121,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M923" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
@@ -39363,6 +43168,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -39400,6 +43210,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M925" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
@@ -39437,6 +43252,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M926" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
@@ -39479,6 +43299,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M927" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P927" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
@@ -39526,6 +43351,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P928" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
@@ -39568,6 +43398,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M929" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
@@ -39605,6 +43440,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
@@ -39642,6 +43482,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M931" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
@@ -39679,6 +43524,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -39716,6 +43566,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -39753,6 +43608,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M934" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -39790,6 +43650,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -39827,6 +43692,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M936" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -39864,6 +43734,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
@@ -39901,6 +43776,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M938" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
@@ -39938,6 +43818,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M939" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
@@ -39975,6 +43860,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
@@ -40012,6 +43902,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
@@ -40049,6 +43944,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M942" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
@@ -40086,6 +43986,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
@@ -40123,6 +44028,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M944" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -40165,6 +44075,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M945" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P945" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
@@ -40212,6 +44127,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M946" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
       <c r="P946" t="inlineStr">
         <is>
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
@@ -40259,6 +44179,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M947" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
@@ -40301,6 +44226,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M948" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
@@ -40333,6 +44263,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M949" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
@@ -40365,6 +44300,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M950" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
@@ -40397,6 +44337,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M951" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -40429,6 +44374,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
@@ -40461,6 +44411,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
@@ -40503,6 +44458,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
@@ -40535,6 +44495,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
@@ -40567,6 +44532,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
@@ -40599,6 +44569,11 @@
           <t>precise</t>
         </is>
       </c>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
@@ -40641,6 +44616,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
@@ -40683,6 +44663,11 @@
           <t>near</t>
         </is>
       </c>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
@@ -40725,6 +44710,11 @@
           <t>inside</t>
         </is>
       </c>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
@@ -40765,6 +44755,11 @@
       <c r="H961" t="inlineStr">
         <is>
           <t>inside</t>
+        </is>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -37688,11 +37688,6 @@
           <t>stazione_carabinieri_castello</t>
         </is>
       </c>
-      <c r="D800" t="inlineStr">
-        <is>
-          <t>gaz_castel_gandolfo</t>
-        </is>
-      </c>
       <c r="E800" t="inlineStr">
         <is>
           <t>santarella</t>
@@ -37706,11 +37701,6 @@
       <c r="G800" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H800" t="inlineStr">
-        <is>
-          <t>inside</t>
         </is>
       </c>
       <c r="M800" t="inlineStr">
@@ -37735,11 +37725,6 @@
           <t>stazione_carabinieri_castello</t>
         </is>
       </c>
-      <c r="D801" t="inlineStr">
-        <is>
-          <t>gaz_castel_gandolfo</t>
-        </is>
-      </c>
       <c r="E801" t="inlineStr">
         <is>
           <t>militi_castello</t>
@@ -37753,11 +37738,6 @@
       <c r="G801" t="inlineStr">
         <is>
           <t>approximate</t>
-        </is>
-      </c>
-      <c r="H801" t="inlineStr">
-        <is>
-          <t>inside</t>
         </is>
       </c>
       <c r="M801" t="inlineStr">

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P961"/>
+  <dimension ref="A1:Q961"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,11 @@
           <t>Critical_Note</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Narrating_Voice_ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10093,6 +10098,11 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10140,6 +10150,11 @@
           <t>La visione del sangue produce uno slittamento semantico tra il personaggio di Ingravallo e un elemento biografico centrale dell'esperienza di Gadda, l'esperienza del fronte e la morte del fratello, attraverso il referente topografico del Cengio e del Faiti</t>
         </is>
       </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -24692,6 +24707,16 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>Voce narrante distinta dal focalizzatore: la voce «tradisce l'incursione del narratore gaddiano» (Perosa 2023a, p. 238).</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -24732,6 +24757,16 @@
       <c r="M505" t="inlineStr">
         <is>
           <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>Voce narrante distinta dal focalizzatore: la voce «tradisce l'incursione del narratore gaddiano» (Perosa 2023a, p. 238).</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>narrator</t>
         </is>
       </c>
     </row>
@@ -30555,6 +30590,16 @@
       <c r="M637" t="inlineStr">
         <is>
           <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>Voce narrante distinta dal focalizzatore: «divaricazione tra voce e punto di vista» (Savettieri 2020, p. 44).</t>
+        </is>
+      </c>
+      <c r="Q637" t="inlineStr">
+        <is>
+          <t>narrator</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -31591,6 +31591,16 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="R660" t="inlineStr">
+        <is>
+          <t>orto_vigna_due_santi</t>
+        </is>
+      </c>
+      <c r="S660" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S960"/>
+  <dimension ref="A1:S962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23215,7 +23215,7 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
+          <t>tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="K471" t="n">
@@ -23260,7 +23260,7 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
+          <t>tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="K472" t="n">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
+          <t>tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="K473" t="n">
@@ -23365,7 +23365,7 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
+          <t>tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="K474" t="n">
@@ -23425,7 +23425,7 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
+          <t>tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="K475" t="n">
@@ -23480,7 +23480,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
+          <t>tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="K476" t="n">
@@ -23505,7 +23505,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>tragitto_torraccio_ponte_divino_amore</t>
+          <t>tragitto_santarella_torraccio_divino_amore</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -30767,6 +30767,19 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>routenode</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>tragitto_sogno_casal_bruciato_campo_morto</t>
+        </is>
+      </c>
+      <c r="K641" t="n">
+        <v>1</v>
+      </c>
       <c r="M641" t="inlineStr">
         <is>
           <t>lorenzo_sabatino</t>
@@ -30814,6 +30827,19 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>routenode</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>tragitto_sogno_casal_bruciato_campo_morto</t>
+        </is>
+      </c>
+      <c r="K642" t="n">
+        <v>2</v>
+      </c>
       <c r="M642" t="inlineStr">
         <is>
           <t>lorenzo_sabatino</t>
@@ -30856,6 +30882,19 @@
           <t>indeterminate</t>
         </is>
       </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>routenode</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>tragitto_sogno_casal_bruciato_campo_morto</t>
+        </is>
+      </c>
+      <c r="K643" t="n">
+        <v>3</v>
+      </c>
       <c r="M643" t="inlineStr">
         <is>
           <t>lorenzo_sabatino</t>
@@ -32444,6 +32483,19 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>routenode</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>tragitto_castel_di_leva_casal_bruciato</t>
+        </is>
+      </c>
+      <c r="K679" t="n">
+        <v>1</v>
+      </c>
       <c r="M679" t="inlineStr">
         <is>
           <t>lorenzo_sabatino</t>
@@ -32486,6 +32538,19 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>routenode</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>tragitto_castel_di_leva_casal_bruciato</t>
+        </is>
+      </c>
+      <c r="K680" t="n">
+        <v>2</v>
+      </c>
       <c r="M680" t="inlineStr">
         <is>
           <t>lorenzo_sabatino</t>
@@ -32528,6 +32593,19 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>routenode</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>tragitto_castel_di_leva_casal_bruciato</t>
+        </is>
+      </c>
+      <c r="K681" t="n">
+        <v>3</v>
+      </c>
       <c r="M681" t="inlineStr">
         <is>
           <t>lorenzo_sabatino</t>
@@ -44805,6 +44883,90 @@
       <c r="M960" t="inlineStr">
         <is>
           <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>interp_00963</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>ref_00728</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>tragitto_sogno_casal_bruciato_campo_morto</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>pestalozzi</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="O961" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>interp_00964</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>ref_00729</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>tragitto_castel_di_leva_casal_bruciato</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>camilla_mattonari</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="O962" t="inlineStr">
+        <is>
+          <t>close_reading</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -33821,7 +33821,7 @@
       </c>
       <c r="P638" t="inlineStr">
         <is>
-          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 212, percorso sognato (Pestalozzi): Manzotti (p. 269) legge «per fil a dest» come un cambio di direzione perpendicolare, in realtà verso sinistra (a sud, verso il Circeo); lettura attribuita, fase 3.</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QPa 212, percorso sognato (Pestalozzi): Manzotti (p. 269) legge «per fil a dest» come un cambio di direzione perpendicolare, in realtà verso sinistra (a sud, verso il Circeo); lettura attribuita, fase 3.</t>
         </is>
       </c>
       <c r="T638" t="inlineStr">
@@ -46350,7 +46350,7 @@
       </c>
       <c r="P893" t="inlineStr">
         <is>
-          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QPa 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
       <c r="R893" t="inlineStr">
@@ -46415,7 +46415,7 @@
       </c>
       <c r="P894" t="inlineStr">
         <is>
-          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QPa 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
       <c r="R894" t="inlineStr">
@@ -46480,7 +46480,7 @@
       </c>
       <c r="P895" t="inlineStr">
         <is>
-          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QPa 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
       <c r="R895" t="inlineStr">
@@ -46545,7 +46545,7 @@
       </c>
       <c r="P896" t="inlineStr">
         <is>
-          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QP 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
+          <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QPa 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
       <c r="R896" t="inlineStr">

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X957"/>
+  <dimension ref="A1:X959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16055,7 +16055,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>ref_00241</t>
+          <t>ref_00733</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -49510,6 +49510,120 @@
         </is>
       </c>
       <c r="T957" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>interp_00965</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>ref_00731</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>sacro_cuore</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>gaz_sacro_cuore</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>luigia_zanchetti</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>marker</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="T958" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>interp_00966</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>ref_00732</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>via_merulana</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>gaz_via_merulana</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>marker</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="O959" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="P959" t="inlineStr">
+        <is>
+          <t>Titolo gridato dagli strilloni: via Merulana nominata come riferimento del delitto, non scena dell'azione; ruolo proposto (D-075).</t>
+        </is>
+      </c>
+      <c r="T959" t="inlineStr">
         <is>
           <t>si</t>
         </is>

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X959"/>
+  <dimension ref="A1:X970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49631,6 +49631,668 @@
         </is>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>interp_00968</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>ref_00737</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>zamira_pacori</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O960" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="P960" t="inlineStr">
+        <is>
+          <t>Il passo colloca la cantina «sotto al laboratorio-bettola» (QPa 165): relazione verticale con il laboratorio, dichiarata qui perché la frase non è nell'estratto (D-091).</t>
+        </is>
+      </c>
+      <c r="R960" t="inlineStr">
+        <is>
+          <t>laboratorio_zamira</t>
+        </is>
+      </c>
+      <c r="S960" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="T960" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>interp_00969</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>ref_00738</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>zamira_pacori</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O961" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T961" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>interp_00970</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>ref_00739</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>sacello_responsale</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>zamira_pacori</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O962" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="P962" t="inlineStr">
+        <is>
+          <t>La sala di consultazione (la cantina) «dava adito», per uscio con catenaccio, al sacello (QPa 165): vani contigui (D-091).</t>
+        </is>
+      </c>
+      <c r="R962" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="S962" t="inlineStr">
+        <is>
+          <t>adjacentto</t>
+        </is>
+      </c>
+      <c r="T962" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>interp_00971</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>ref_00740</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>zamira_pacori</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M963" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O963" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T963" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>interp_00972</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>ref_00741</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>zamira_pacori</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O964" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T964" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>interp_00973</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>ref_00741</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>santarella</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O965" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T965" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>interp_00974</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>ref_00742</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>zamira_pacori</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>projectedspace</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M966" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O966" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T966" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>interp_00975</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>ref_00742</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>diomede</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>projectedspace</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M967" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N967" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O967" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T967" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>interp_00976</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>ref_00743</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>zamira_pacori</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>projectedspace</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>indeterminate</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M968" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O968" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T968" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>interp_00977</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>ref_00743</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>diomede</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>projectedspace</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>indeterminate</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M969" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N969" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O969" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T969" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>interp_00978</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>ref_00744</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>camera_sicurezza_questura</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>gaz_santo_stefano_del_cacco_celio_santo_stefano</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>ines_cionini</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>projectedspace</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M970" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O970" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T970" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X970"/>
+  <dimension ref="A1:X969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49659,7 +49659,7 @@
       </c>
       <c r="G960" t="inlineStr">
         <is>
-          <t>relative</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="H960" t="inlineStr">
@@ -49680,21 +49680,6 @@
       <c r="O960" t="inlineStr">
         <is>
           <t>close_reading</t>
-        </is>
-      </c>
-      <c r="P960" t="inlineStr">
-        <is>
-          <t>Il passo colloca la cantina «sotto al laboratorio-bettola» (QPa 165): relazione verticale con il laboratorio, dichiarata qui perché la frase non è nell'estratto (D-091).</t>
-        </is>
-      </c>
-      <c r="R960" t="inlineStr">
-        <is>
-          <t>laboratorio_zamira</t>
-        </is>
-      </c>
-      <c r="S960" t="inlineStr">
-        <is>
-          <t>below</t>
         </is>
       </c>
       <c r="T960" t="inlineStr">
@@ -49940,6 +49925,21 @@
           <t>close_reading</t>
         </is>
       </c>
+      <c r="P964" t="inlineStr">
+        <is>
+          <t>La Zamira manda a «levarseli in cantina» e a portare i pantaloni «su […] in laboratorio» (QPa 169): la cantina sta sotto il laboratorio (D-091).</t>
+        </is>
+      </c>
+      <c r="R964" t="inlineStr">
+        <is>
+          <t>laboratorio_zamira</t>
+        </is>
+      </c>
+      <c r="S964" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
       <c r="T964" t="inlineStr">
         <is>
           <t>si</t>
@@ -49949,12 +49949,12 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>interp_00973</t>
+          <t>interp_00974</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>ref_00741</t>
+          <t>ref_00742</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -49964,17 +49964,17 @@
       </c>
       <c r="E965" t="inlineStr">
         <is>
-          <t>santarella</t>
+          <t>zamira_pacori</t>
         </is>
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>setting</t>
+          <t>projectedspace</t>
         </is>
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>relative</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
@@ -50006,7 +50006,7 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>interp_00974</t>
+          <t>interp_00975</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
@@ -50021,7 +50021,7 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>zamira_pacori</t>
+          <t>diomede</t>
         </is>
       </c>
       <c r="F966" t="inlineStr">
@@ -50063,12 +50063,12 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>interp_00975</t>
+          <t>interp_00976</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>ref_00742</t>
+          <t>ref_00743</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
@@ -50078,7 +50078,7 @@
       </c>
       <c r="E967" t="inlineStr">
         <is>
-          <t>diomede</t>
+          <t>zamira_pacori</t>
         </is>
       </c>
       <c r="F967" t="inlineStr">
@@ -50088,7 +50088,7 @@
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>approximate</t>
+          <t>indeterminate</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
@@ -50120,7 +50120,7 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>interp_00976</t>
+          <t>interp_00977</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
@@ -50135,7 +50135,7 @@
       </c>
       <c r="E968" t="inlineStr">
         <is>
-          <t>zamira_pacori</t>
+          <t>diomede</t>
         </is>
       </c>
       <c r="F968" t="inlineStr">
@@ -50177,22 +50177,27 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>interp_00977</t>
+          <t>interp_00978</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>ref_00743</t>
+          <t>ref_00744</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>cantina_zamira</t>
+          <t>camera_sicurezza_questura</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>gaz_santo_stefano_del_cacco_celio_santo_stefano</t>
         </is>
       </c>
       <c r="E969" t="inlineStr">
         <is>
-          <t>diomede</t>
+          <t>ines_cionini</t>
         </is>
       </c>
       <c r="F969" t="inlineStr">
@@ -50202,7 +50207,7 @@
       </c>
       <c r="G969" t="inlineStr">
         <is>
-          <t>indeterminate</t>
+          <t>approximate</t>
         </is>
       </c>
       <c r="H969" t="inlineStr">
@@ -50226,68 +50231,6 @@
         </is>
       </c>
       <c r="T969" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-    </row>
-    <row r="970">
-      <c r="A970" t="inlineStr">
-        <is>
-          <t>interp_00978</t>
-        </is>
-      </c>
-      <c r="B970" t="inlineStr">
-        <is>
-          <t>ref_00744</t>
-        </is>
-      </c>
-      <c r="C970" t="inlineStr">
-        <is>
-          <t>camera_sicurezza_questura</t>
-        </is>
-      </c>
-      <c r="D970" t="inlineStr">
-        <is>
-          <t>gaz_santo_stefano_del_cacco_celio_santo_stefano</t>
-        </is>
-      </c>
-      <c r="E970" t="inlineStr">
-        <is>
-          <t>ines_cionini</t>
-        </is>
-      </c>
-      <c r="F970" t="inlineStr">
-        <is>
-          <t>projectedspace</t>
-        </is>
-      </c>
-      <c r="G970" t="inlineStr">
-        <is>
-          <t>approximate</t>
-        </is>
-      </c>
-      <c r="H970" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="M970" t="inlineStr">
-        <is>
-          <t>lorenzo_sabatino</t>
-        </is>
-      </c>
-      <c r="N970" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="O970" t="inlineStr">
-        <is>
-          <t>close_reading</t>
-        </is>
-      </c>
-      <c r="T970" t="inlineStr">
         <is>
           <t>si</t>
         </is>

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X969"/>
+  <dimension ref="A1:X973"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -29385,7 +29385,7 @@
       </c>
       <c r="T549" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -29437,7 +29437,7 @@
       </c>
       <c r="T550" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -43212,7 +43212,7 @@
       </c>
       <c r="T830" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -50233,6 +50233,282 @@
       <c r="T969" t="inlineStr">
         <is>
           <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>interp_00979</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>ref_00028</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>via_delle_oche</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>gaz_via_delle_oche_milano</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>ingravallo</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>projectedspace</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
+      <c r="M970" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O970" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="P970" t="inlineStr">
+        <is>
+          <t>Possibile suggestione della via delle Oche di Bologna, nota per le case chiuse: lettura dell'autore, che non incide su statuto e collocazione.</t>
+        </is>
+      </c>
+      <c r="T970" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="V970" t="inlineStr">
+        <is>
+          <t>interp_00029</t>
+        </is>
+      </c>
+      <c r="W970" t="inlineStr">
+        <is>
+          <t>terzoli_2015</t>
+        </is>
+      </c>
+      <c r="X970" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>interp_00980</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>ref_00466</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>pensione_burgess</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>gaz_roma</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>americana_inglese</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>projectedspace</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>indeterminate</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M971" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N971" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O971" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T971" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="V971" t="inlineStr">
+        <is>
+          <t>interp_00552</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>interp_00981</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>ref_00467</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>pensione_burgess</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>gaz_roma</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>pompeo</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>projectedspace</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>indeterminate</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M972" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N972" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O972" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T972" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="V972" t="inlineStr">
+        <is>
+          <t>interp_00553</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>interp_00982</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>ref_00671</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>pensione_burgess</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>gaz_roma</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>pompeo</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>marker</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>indeterminate</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="M973" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N973" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O973" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="T973" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="V973" t="inlineStr">
+        <is>
+          <t>interp_00836</t>
         </is>
       </c>
     </row>

--- a/data/source/xlsx/SpatialInterpretations.xlsx
+++ b/data/source/xlsx/SpatialInterpretations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X973"/>
+  <dimension ref="A1:W975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,40 +499,35 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Narrating_Voice_ID</t>
+          <t>Relational_Anchor_IDs</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Relational_Anchor_IDs</t>
+          <t>Relational_Anchor_Type</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Relational_Anchor_Type</t>
+          <t>Adopted</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Adopted</t>
+          <t>Reading_Author_ID</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Reading_Author_ID</t>
+          <t>Revision_Of</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Revision_Of</t>
+          <t>Source_ID</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
-        <is>
-          <t>Source_ID</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
         <is>
           <t>Source_Page</t>
         </is>
@@ -604,7 +599,7 @@
           <t>La “collina molisana” è impiegata come sineddoche spaziale dell’origine sociale del personaggio; lo spazio non è diegeticamente attivo ma funziona come proiezione identitaria e culturale.</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -666,7 +661,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -728,7 +723,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -790,7 +785,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -862,7 +857,7 @@
           <t>Generico Barbiere</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -929,7 +924,7 @@
           <t>Luogo generico</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1001,7 +996,7 @@
           <t>Palazzo del "fattaccio", in cui prende luogo l'evento principale del romanzo</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1073,7 +1068,7 @@
           <t>Palazzo del "fattaccio", in cui prende luogo l'evento principale del romanzo</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1140,7 +1135,7 @@
           <t>Scala A e Scala B del palazzo, a riflettere la simmetria imperfetta che alligna nel Palazzo</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1207,7 +1202,7 @@
           <t>Scala A del palazzo, in cui si realizzeranno i due crimini centrali del romanzo</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1274,7 +1269,7 @@
           <t>Aggettivo che evoca lo spazio dei Colli Albani/Castelli Romani</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1341,7 +1336,7 @@
           <t>Aggettivo che evoca lo spazio di Tivoli</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1403,7 +1398,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1465,7 +1460,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1527,7 +1522,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1589,7 +1584,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1656,7 +1651,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1718,7 +1713,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1780,7 +1775,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1842,7 +1837,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1904,7 +1899,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1966,7 +1961,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2033,7 +2028,7 @@
           <t>Monteleone, probabilmente Monteleone sabino, indicato come luogo d'origine d'una delle "nipotine" al servizio dei Balducci</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2100,7 +2095,7 @@
           <t>Anzio si collona nel territorio costiero del Castelli Romani</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2172,7 +2167,7 @@
           <t>Area paesaggistica vaga e analogica, delimitata dal Tevere e costruita per accumulo descrittivo (castelli, vigne, colli, monti, piane), contrapposta alla città di Roma; spazio percepito e mitizzato da Liliana Balducci. Il Tevere funziona come barriera idrografica e simbolica di separazione tra spazio urbano e spazio campestre, più che come luogo in sé.</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2234,7 +2229,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2306,7 +2301,7 @@
           <t>Palazzo del "fattaccio", in cui prende luogo l'evento principale del romanzo</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2378,7 +2373,7 @@
           <t>L’espressione «via delle Oche», riferita a Milano, non risulta attestata nella toponomastica urbana storica. Il toponimo può essere interpretato come una trasposizione simbolica e ironica della via delle Oche bolognese, luogo storicamente associato alla prostituzione e alla cultura popolare femminile. Il contesto discorsivo (la figura della «ragazza» e il riferimento al «dispensario celtico» come "luogo di marginalità femminile travestito da antropologia nordica") suggerisce un uso allusivo e deformante dello spazio urbano, coerente con la pratica gaddiana di sovrapposizione e travestimento topografico. Il riferimento non va quindi inteso in senso referenziale, ma come costruzione narrativa a forte densità simbolica (prostituzione, oralità popolare, corpo femminile).</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -2440,7 +2435,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2512,7 +2507,7 @@
           <t>Palazzo del "fattaccio", in cui prende luogo l'evento principale del romanzo</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2574,7 +2569,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2636,7 +2631,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2698,7 +2693,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2763,7 +2758,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2828,7 +2823,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2893,7 +2888,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -2958,7 +2953,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3023,7 +3018,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3088,7 +3083,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3163,7 +3158,7 @@
           <t>Palazzo del "fattaccio", in cui prende luogo l'evento principale del romanzo</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3238,7 +3233,7 @@
           <t>Palazzo del "fattaccio", in cui prende luogo l'evento principale del romanzo</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3313,7 +3308,7 @@
           <t>Palazzo del "fattaccio", in cui prende luogo l'evento principale del romanzo</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3375,7 +3370,7 @@
           <t>Percorso di Ingravallo, Gaudenzio e Pompeo</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3437,7 +3432,7 @@
           <t>Percorso di Ingravallo, Gaudenzio e Pompeo</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3499,7 +3494,7 @@
           <t>Percorso di Ingravallo, Gaudenzio e Pompeo</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3571,7 +3566,7 @@
           <t>Palazzo del "fattaccio", in cui prende luogo l'evento principale del romanzo</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3643,7 +3638,7 @@
           <t>Palazzo del "fattaccio", in cui prende luogo l'evento principale del romanzo</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3715,7 +3710,7 @@
           <t>Palazzo del "fattaccio", in cui prende luogo l'evento principale del romanzo</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3787,7 +3782,7 @@
           <t>L’espressione «la ben nota architettura» costituisce una perifrasi eufemistica e allusiva riferita al palazzo di via Merulana (civico 219), già più volte menzionato nel romanzo attraverso denominazioni varianti. L’identificazione non è letterale né nominativa, ma si fonda sulla ricorrenza contestuale, sulla focalizzazione interna (Ingravallo) e sul valore di riconoscibilità implicita attribuito al luogo, che assume qui una funzione evocativa e psicologica più che descrittiva o topografica.</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3859,7 +3854,7 @@
           <t>L’espressione «casermone color pidocchio» costituisce una perifrasi eufemistica e allusiva riferita al palazzo di via Merulana (civico 219), già più volte menzionato nel romanzo attraverso denominazioni varianti.</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -3931,7 +3926,7 @@
           <t>L’espressione «casermone color pidocchio» costituisce una perifrasi eufemistica e allusiva riferita al palazzo di via Merulana (civico 219), già più volte menzionato nel romanzo attraverso denominazioni varianti.</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4003,7 +3998,7 @@
           <t>L’espressione «casermone color pidocchio» costituisce una perifrasi eufemistica e allusiva riferita al palazzo di via Merulana (civico 219), già più volte menzionato nel romanzo attraverso denominazioni varianti.</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4075,7 +4070,7 @@
           <t>L’espressione «sto palazzo» costituisce una perifrasi eufemistica e allusiva riferita al palazzo di via Merulana (civico 219), già più volte menzionato nel romanzo attraverso denominazioni varianti.</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4137,7 +4132,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4204,7 +4199,7 @@
           <t>Scala A del palazzo, in cui si realizzeranno i due crimini centrali del romanzo</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4266,7 +4261,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4333,7 +4328,7 @@
           <t>Piani alti della Scala A, palazzo 219</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4405,7 +4400,7 @@
           <t>Palazzo del "fattaccio", in cui prende luogo l'evento principale del romanzo</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4472,7 +4467,7 @@
           <t>Scala A e Scala B del palazzo, a riflettere la simmetria imperfetta che alligna nel Palazzo</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4539,7 +4534,7 @@
           <t>Scala A del palazzo, in cui si realizzeranno i due crimini centrali del romanzo</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4601,7 +4596,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4668,7 +4663,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4730,7 +4725,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4792,7 +4787,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4854,7 +4849,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4916,7 +4911,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -4978,7 +4973,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5040,7 +5035,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5102,7 +5097,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5164,7 +5159,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5226,7 +5221,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5298,7 +5293,7 @@
           <t>Palazzo del "fattaccio"</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5360,7 +5355,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5422,7 +5417,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5487,7 +5482,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5552,7 +5547,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5617,7 +5612,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5682,7 +5677,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5747,7 +5742,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5804,7 +5799,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5869,7 +5864,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5934,7 +5929,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -5999,7 +5994,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6064,7 +6059,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6129,7 +6124,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6196,7 +6191,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6253,7 +6248,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6318,7 +6313,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6383,7 +6378,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6448,7 +6443,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T91" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6505,7 +6500,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6567,7 +6562,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6629,7 +6624,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6691,7 +6686,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6758,7 +6753,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6820,7 +6815,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6882,7 +6877,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -6944,7 +6939,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T99" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7006,7 +7001,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T100" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7068,7 +7063,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="S101" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7140,7 +7135,7 @@
           <t>Tevere e Biferno sono impiegati come sineddoche spaziale dei tratti diatopici della lingua di Ingravallo</t>
         </is>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="S102" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7202,7 +7197,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T103" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7264,7 +7259,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T104" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7326,7 +7321,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T105" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7388,7 +7383,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T106" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7450,7 +7445,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T107" t="inlineStr">
+      <c r="S107" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7512,7 +7507,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T108" t="inlineStr">
+      <c r="S108" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7574,7 +7569,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="S109" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7636,7 +7631,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr">
+      <c r="S110" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7703,7 +7698,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T111" t="inlineStr">
+      <c r="S111" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7765,7 +7760,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T112" t="inlineStr">
+      <c r="S112" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7827,7 +7822,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T113" t="inlineStr">
+      <c r="S113" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7889,7 +7884,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T114" t="inlineStr">
+      <c r="S114" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -7951,7 +7946,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T115" t="inlineStr">
+      <c r="S115" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8013,7 +8008,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T116" t="inlineStr">
+      <c r="S116" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8075,7 +8070,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T117" t="inlineStr">
+      <c r="S117" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8137,7 +8132,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T118" t="inlineStr">
+      <c r="S118" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8199,7 +8194,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T119" t="inlineStr">
+      <c r="S119" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8261,7 +8256,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T120" t="inlineStr">
+      <c r="S120" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8323,7 +8318,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T121" t="inlineStr">
+      <c r="S121" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8385,7 +8380,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T122" t="inlineStr">
+      <c r="S122" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8447,7 +8442,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T123" t="inlineStr">
+      <c r="S123" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8509,7 +8504,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T124" t="inlineStr">
+      <c r="S124" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8571,7 +8566,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T125" t="inlineStr">
+      <c r="S125" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8633,7 +8628,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T126" t="inlineStr">
+      <c r="S126" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8695,7 +8690,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="S127" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8757,7 +8752,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T128" t="inlineStr">
+      <c r="S128" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8819,7 +8814,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T129" t="inlineStr">
+      <c r="S129" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8886,7 +8881,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T130" t="inlineStr">
+      <c r="S130" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -8948,7 +8943,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T131" t="inlineStr">
+      <c r="S131" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9010,7 +9005,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T132" t="inlineStr">
+      <c r="S132" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9072,7 +9067,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T133" t="inlineStr">
+      <c r="S133" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9134,7 +9129,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T134" t="inlineStr">
+      <c r="S134" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9196,7 +9191,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T135" t="inlineStr">
+      <c r="S135" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9258,7 +9253,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T136" t="inlineStr">
+      <c r="S136" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9320,7 +9315,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T137" t="inlineStr">
+      <c r="S137" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9382,7 +9377,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T138" t="inlineStr">
+      <c r="S138" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9444,7 +9439,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T139" t="inlineStr">
+      <c r="S139" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9506,7 +9501,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T140" t="inlineStr">
+      <c r="S140" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9568,7 +9563,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T141" t="inlineStr">
+      <c r="S141" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9630,7 +9625,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T142" t="inlineStr">
+      <c r="S142" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9687,7 +9682,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T143" t="inlineStr">
+      <c r="S143" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9734,7 +9729,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T144" t="inlineStr">
+      <c r="S144" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9781,7 +9776,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T145" t="inlineStr">
+      <c r="S145" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9828,7 +9823,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T146" t="inlineStr">
+      <c r="S146" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9880,7 +9875,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T147" t="inlineStr">
+      <c r="S147" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9927,7 +9922,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T148" t="inlineStr">
+      <c r="S148" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -9974,7 +9969,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T149" t="inlineStr">
+      <c r="S149" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10021,7 +10016,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T150" t="inlineStr">
+      <c r="S150" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10071,7 +10066,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T151" t="inlineStr">
+      <c r="S151" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10121,7 +10116,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T152" t="inlineStr">
+      <c r="S152" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10171,7 +10166,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T153" t="inlineStr">
+      <c r="S153" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10213,7 +10208,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T154" t="inlineStr">
+      <c r="S154" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10260,7 +10255,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T155" t="inlineStr">
+      <c r="S155" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10307,7 +10302,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T156" t="inlineStr">
+      <c r="S156" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10354,7 +10349,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T157" t="inlineStr">
+      <c r="S157" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10401,7 +10396,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T158" t="inlineStr">
+      <c r="S158" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10448,7 +10443,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T159" t="inlineStr">
+      <c r="S159" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10495,7 +10490,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T160" t="inlineStr">
+      <c r="S160" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10542,7 +10537,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T161" t="inlineStr">
+      <c r="S161" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10589,7 +10584,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T162" t="inlineStr">
+      <c r="S162" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10636,7 +10631,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T163" t="inlineStr">
+      <c r="S163" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10683,7 +10678,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T164" t="inlineStr">
+      <c r="S164" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10730,7 +10725,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T165" t="inlineStr">
+      <c r="S165" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10777,7 +10772,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T166" t="inlineStr">
+      <c r="S166" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10824,12 +10819,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="Q167" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="T167" t="inlineStr">
+      <c r="S167" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10881,12 +10871,7 @@
           <t>La visione del sangue produce uno slittamento semantico tra il personaggio di Ingravallo e un elemento biografico centrale dell'esperienza di Gadda, l'esperienza del fronte e la morte del fratello, attraverso il referente topografico del Cengio e del Faiti</t>
         </is>
       </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="T168" t="inlineStr">
+      <c r="S168" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10933,7 +10918,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T169" t="inlineStr">
+      <c r="S169" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -10980,7 +10965,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T170" t="inlineStr">
+      <c r="S170" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11027,7 +11012,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T171" t="inlineStr">
+      <c r="S171" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11074,7 +11059,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T172" t="inlineStr">
+      <c r="S172" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11121,7 +11106,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T173" t="inlineStr">
+      <c r="S173" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11168,7 +11153,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T174" t="inlineStr">
+      <c r="S174" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11215,7 +11200,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T175" t="inlineStr">
+      <c r="S175" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11262,7 +11247,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T176" t="inlineStr">
+      <c r="S176" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11314,7 +11299,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T177" t="inlineStr">
+      <c r="S177" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11361,7 +11346,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T178" t="inlineStr">
+      <c r="S178" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11408,7 +11393,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T179" t="inlineStr">
+      <c r="S179" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11455,7 +11440,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T180" t="inlineStr">
+      <c r="S180" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11502,7 +11487,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T181" t="inlineStr">
+      <c r="S181" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11554,7 +11539,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T182" t="inlineStr">
+      <c r="S182" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11606,7 +11591,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T183" t="inlineStr">
+      <c r="S183" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11658,7 +11643,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T184" t="inlineStr">
+      <c r="S184" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11710,7 +11695,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T185" t="inlineStr">
+      <c r="S185" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11762,7 +11747,7 @@
           <t>Il monte rappresenta per sineddoche l'origine molisana del protagonista</t>
         </is>
       </c>
-      <c r="T186" t="inlineStr">
+      <c r="S186" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11809,7 +11794,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T187" t="inlineStr">
+      <c r="S187" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11856,7 +11841,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T188" t="inlineStr">
+      <c r="S188" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11903,7 +11888,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T189" t="inlineStr">
+      <c r="S189" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11950,7 +11935,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T190" t="inlineStr">
+      <c r="S190" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -11997,7 +11982,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T191" t="inlineStr">
+      <c r="S191" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12044,7 +12029,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T192" t="inlineStr">
+      <c r="S192" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12091,7 +12076,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T193" t="inlineStr">
+      <c r="S193" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12138,7 +12123,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T194" t="inlineStr">
+      <c r="S194" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12185,7 +12170,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T195" t="inlineStr">
+      <c r="S195" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12232,7 +12217,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T196" t="inlineStr">
+      <c r="S196" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12279,7 +12264,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T197" t="inlineStr">
+      <c r="S197" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12326,7 +12311,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T198" t="inlineStr">
+      <c r="S198" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12373,7 +12358,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T199" t="inlineStr">
+      <c r="S199" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12420,7 +12405,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T200" t="inlineStr">
+      <c r="S200" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12467,7 +12452,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T201" t="inlineStr">
+      <c r="S201" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12514,7 +12499,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T202" t="inlineStr">
+      <c r="S202" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12561,7 +12546,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T203" t="inlineStr">
+      <c r="S203" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12618,7 +12603,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T204" t="inlineStr">
+      <c r="S204" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12665,7 +12650,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T205" t="inlineStr">
+      <c r="S205" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12712,7 +12697,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T206" t="inlineStr">
+      <c r="S206" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12759,7 +12744,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T207" t="inlineStr">
+      <c r="S207" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12806,7 +12791,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T208" t="inlineStr">
+      <c r="S208" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12858,7 +12843,7 @@
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
         </is>
       </c>
-      <c r="T209" t="inlineStr">
+      <c r="S209" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12910,7 +12895,7 @@
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
         </is>
       </c>
-      <c r="T210" t="inlineStr">
+      <c r="S210" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -12962,7 +12947,7 @@
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
         </is>
       </c>
-      <c r="T211" t="inlineStr">
+      <c r="S211" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13014,7 +12999,7 @@
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
         </is>
       </c>
-      <c r="T212" t="inlineStr">
+      <c r="S212" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13066,7 +13051,7 @@
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
         </is>
       </c>
-      <c r="T213" t="inlineStr">
+      <c r="S213" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13123,7 +13108,7 @@
           <t>Le nerovestite costituisce un nome collettivo orientato a caratterizzare genericamente lo spettro femminile di donne che, a vario titolo, gravitarono nell'orbita dalla fascinazione fascista</t>
         </is>
       </c>
-      <c r="T214" t="inlineStr">
+      <c r="S214" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13175,7 +13160,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T215" t="inlineStr">
+      <c r="S215" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13227,7 +13212,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T216" t="inlineStr">
+      <c r="S216" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13274,7 +13259,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T217" t="inlineStr">
+      <c r="S217" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13321,7 +13306,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T218" t="inlineStr">
+      <c r="S218" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13368,7 +13353,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T219" t="inlineStr">
+      <c r="S219" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13415,7 +13400,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T220" t="inlineStr">
+      <c r="S220" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13462,7 +13447,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T221" t="inlineStr">
+      <c r="S221" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13509,7 +13494,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T222" t="inlineStr">
+      <c r="S222" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13556,7 +13541,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T223" t="inlineStr">
+      <c r="S223" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13603,7 +13588,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T224" t="inlineStr">
+      <c r="S224" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13650,7 +13635,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T225" t="inlineStr">
+      <c r="S225" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13697,7 +13682,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T226" t="inlineStr">
+      <c r="S226" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13744,7 +13729,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T227" t="inlineStr">
+      <c r="S227" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13791,7 +13776,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T228" t="inlineStr">
+      <c r="S228" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13838,7 +13823,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T229" t="inlineStr">
+      <c r="S229" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13885,7 +13870,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T230" t="inlineStr">
+      <c r="S230" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13932,7 +13917,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T231" t="inlineStr">
+      <c r="S231" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -13979,7 +13964,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T232" t="inlineStr">
+      <c r="S232" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14026,7 +14011,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T233" t="inlineStr">
+      <c r="S233" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14073,7 +14058,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T234" t="inlineStr">
+      <c r="S234" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14120,7 +14105,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T235" t="inlineStr">
+      <c r="S235" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14172,7 +14157,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T236" t="inlineStr">
+      <c r="S236" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14224,7 +14209,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T237" t="inlineStr">
+      <c r="S237" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14271,7 +14256,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T238" t="inlineStr">
+      <c r="S238" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14318,7 +14303,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T239" t="inlineStr">
+      <c r="S239" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14365,7 +14350,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T240" t="inlineStr">
+      <c r="S240" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14412,7 +14397,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T241" t="inlineStr">
+      <c r="S241" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14459,7 +14444,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T242" t="inlineStr">
+      <c r="S242" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14506,7 +14491,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T243" t="inlineStr">
+      <c r="S243" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14553,7 +14538,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T244" t="inlineStr">
+      <c r="S244" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14600,7 +14585,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T245" t="inlineStr">
+      <c r="S245" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14647,7 +14632,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T246" t="inlineStr">
+      <c r="S246" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14694,7 +14679,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T247" t="inlineStr">
+      <c r="S247" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14744,7 +14729,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T248" t="inlineStr">
+      <c r="S248" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14794,7 +14779,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T249" t="inlineStr">
+      <c r="S249" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14836,7 +14821,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T250" t="inlineStr">
+      <c r="S250" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14883,7 +14868,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T251" t="inlineStr">
+      <c r="S251" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14930,7 +14915,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T252" t="inlineStr">
+      <c r="S252" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -14977,7 +14962,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T253" t="inlineStr">
+      <c r="S253" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15024,7 +15009,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T254" t="inlineStr">
+      <c r="S254" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15071,7 +15056,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T255" t="inlineStr">
+      <c r="S255" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15118,7 +15103,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T256" t="inlineStr">
+      <c r="S256" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15165,7 +15150,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T257" t="inlineStr">
+      <c r="S257" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15212,7 +15197,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T258" t="inlineStr">
+      <c r="S258" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15259,7 +15244,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T259" t="inlineStr">
+      <c r="S259" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15306,7 +15291,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T260" t="inlineStr">
+      <c r="S260" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15353,7 +15338,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T261" t="inlineStr">
+      <c r="S261" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15400,7 +15385,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T262" t="inlineStr">
+      <c r="S262" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15447,7 +15432,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T263" t="inlineStr">
+      <c r="S263" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15494,7 +15479,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T264" t="inlineStr">
+      <c r="S264" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15541,7 +15526,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T265" t="inlineStr">
+      <c r="S265" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15588,7 +15573,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T266" t="inlineStr">
+      <c r="S266" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15635,7 +15620,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T267" t="inlineStr">
+      <c r="S267" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15687,7 +15672,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T268" t="inlineStr">
+      <c r="S268" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15739,7 +15724,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T269" t="inlineStr">
+      <c r="S269" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15791,7 +15776,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T270" t="inlineStr">
+      <c r="S270" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15843,7 +15828,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T271" t="inlineStr">
+      <c r="S271" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15890,7 +15875,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T272" t="inlineStr">
+      <c r="S272" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15942,7 +15927,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T273" t="inlineStr">
+      <c r="S273" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -15994,7 +15979,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T274" t="inlineStr">
+      <c r="S274" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16041,7 +16026,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T275" t="inlineStr">
+      <c r="S275" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16088,7 +16073,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T276" t="inlineStr">
+      <c r="S276" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16140,7 +16125,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T277" t="inlineStr">
+      <c r="S277" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16202,7 +16187,7 @@
           <t>2026-04-08 00:00:00</t>
         </is>
       </c>
-      <c r="T278" t="inlineStr">
+      <c r="S278" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16264,7 +16249,7 @@
           <t>2026-04-08 00:00:00</t>
         </is>
       </c>
-      <c r="T279" t="inlineStr">
+      <c r="S279" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16316,7 +16301,7 @@
           <t>05.05.26</t>
         </is>
       </c>
-      <c r="T280" t="inlineStr">
+      <c r="S280" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16363,7 +16348,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T281" t="inlineStr">
+      <c r="S281" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16410,7 +16395,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T282" t="inlineStr">
+      <c r="S282" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16457,7 +16442,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T283" t="inlineStr">
+      <c r="S283" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16504,7 +16489,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T284" t="inlineStr">
+      <c r="S284" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16551,7 +16536,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T285" t="inlineStr">
+      <c r="S285" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16603,7 +16588,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T286" t="inlineStr">
+      <c r="S286" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16650,7 +16635,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T287" t="inlineStr">
+      <c r="S287" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16697,7 +16682,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T288" t="inlineStr">
+      <c r="S288" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16744,7 +16729,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T289" t="inlineStr">
+      <c r="S289" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16791,7 +16776,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T290" t="inlineStr">
+      <c r="S290" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16838,7 +16823,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T291" t="inlineStr">
+      <c r="S291" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16885,7 +16870,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T292" t="inlineStr">
+      <c r="S292" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16932,7 +16917,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T293" t="inlineStr">
+      <c r="S293" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -16979,7 +16964,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T294" t="inlineStr">
+      <c r="S294" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17026,7 +17011,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T295" t="inlineStr">
+      <c r="S295" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17073,7 +17058,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T296" t="inlineStr">
+      <c r="S296" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17120,7 +17105,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T297" t="inlineStr">
+      <c r="S297" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17167,7 +17152,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T298" t="inlineStr">
+      <c r="S298" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17214,7 +17199,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T299" t="inlineStr">
+      <c r="S299" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17261,7 +17246,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T300" t="inlineStr">
+      <c r="S300" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17308,7 +17293,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T301" t="inlineStr">
+      <c r="S301" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17355,7 +17340,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T302" t="inlineStr">
+      <c r="S302" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17402,7 +17387,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T303" t="inlineStr">
+      <c r="S303" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17449,7 +17434,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T304" t="inlineStr">
+      <c r="S304" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17496,7 +17481,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T305" t="inlineStr">
+      <c r="S305" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17543,7 +17528,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T306" t="inlineStr">
+      <c r="S306" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17590,7 +17575,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T307" t="inlineStr">
+      <c r="S307" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17637,7 +17622,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T308" t="inlineStr">
+      <c r="S308" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17684,7 +17669,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T309" t="inlineStr">
+      <c r="S309" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17731,7 +17716,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T310" t="inlineStr">
+      <c r="S310" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17778,7 +17763,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T311" t="inlineStr">
+      <c r="S311" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17825,7 +17810,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T312" t="inlineStr">
+      <c r="S312" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17872,7 +17857,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T313" t="inlineStr">
+      <c r="S313" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17919,7 +17904,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T314" t="inlineStr">
+      <c r="S314" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -17966,7 +17951,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T315" t="inlineStr">
+      <c r="S315" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18013,7 +17998,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T316" t="inlineStr">
+      <c r="S316" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18060,7 +18045,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T317" t="inlineStr">
+      <c r="S317" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18107,7 +18092,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T318" t="inlineStr">
+      <c r="S318" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18154,7 +18139,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T319" t="inlineStr">
+      <c r="S319" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18201,7 +18186,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T320" t="inlineStr">
+      <c r="S320" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18248,7 +18233,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T321" t="inlineStr">
+      <c r="S321" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18295,7 +18280,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T322" t="inlineStr">
+      <c r="S322" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18347,7 +18332,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T323" t="inlineStr">
+      <c r="S323" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18399,7 +18384,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T324" t="inlineStr">
+      <c r="S324" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18451,7 +18436,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T325" t="inlineStr">
+      <c r="S325" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18503,7 +18488,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T326" t="inlineStr">
+      <c r="S326" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18550,7 +18535,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T327" t="inlineStr">
+      <c r="S327" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18597,7 +18582,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T328" t="inlineStr">
+      <c r="S328" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18644,7 +18629,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T329" t="inlineStr">
+      <c r="S329" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18691,7 +18676,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T330" t="inlineStr">
+      <c r="S330" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18738,7 +18723,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T331" t="inlineStr">
+      <c r="S331" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18785,7 +18770,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T332" t="inlineStr">
+      <c r="S332" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18832,7 +18817,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T333" t="inlineStr">
+      <c r="S333" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18879,7 +18864,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T334" t="inlineStr">
+      <c r="S334" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18926,7 +18911,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T335" t="inlineStr">
+      <c r="S335" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -18973,7 +18958,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T336" t="inlineStr">
+      <c r="S336" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19020,7 +19005,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T337" t="inlineStr">
+      <c r="S337" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19067,7 +19052,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T338" t="inlineStr">
+      <c r="S338" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19114,7 +19099,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T339" t="inlineStr">
+      <c r="S339" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19161,7 +19146,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T340" t="inlineStr">
+      <c r="S340" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19208,7 +19193,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T341" t="inlineStr">
+      <c r="S341" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19255,7 +19240,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T342" t="inlineStr">
+      <c r="S342" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19302,7 +19287,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T343" t="inlineStr">
+      <c r="S343" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19349,7 +19334,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T344" t="inlineStr">
+      <c r="S344" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19396,7 +19381,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T345" t="inlineStr">
+      <c r="S345" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19443,7 +19428,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T346" t="inlineStr">
+      <c r="S346" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19490,7 +19475,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T347" t="inlineStr">
+      <c r="S347" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19537,7 +19522,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T348" t="inlineStr">
+      <c r="S348" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19587,7 +19572,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T349" t="inlineStr">
+      <c r="S349" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19637,7 +19622,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T350" t="inlineStr">
+      <c r="S350" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19687,7 +19672,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T351" t="inlineStr">
+      <c r="S351" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19729,7 +19714,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T352" t="inlineStr">
+      <c r="S352" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19781,7 +19766,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T353" t="inlineStr">
+      <c r="S353" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19828,7 +19813,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T354" t="inlineStr">
+      <c r="S354" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19880,7 +19865,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T355" t="inlineStr">
+      <c r="S355" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19927,7 +19912,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T356" t="inlineStr">
+      <c r="S356" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -19974,7 +19959,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T357" t="inlineStr">
+      <c r="S357" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20021,7 +20006,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T358" t="inlineStr">
+      <c r="S358" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20068,7 +20053,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T359" t="inlineStr">
+      <c r="S359" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20115,7 +20100,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T360" t="inlineStr">
+      <c r="S360" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20162,7 +20147,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T361" t="inlineStr">
+      <c r="S361" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20209,7 +20194,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T362" t="inlineStr">
+      <c r="S362" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20256,7 +20241,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T363" t="inlineStr">
+      <c r="S363" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20308,7 +20293,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T364" t="inlineStr">
+      <c r="S364" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20360,7 +20345,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T365" t="inlineStr">
+      <c r="S365" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20412,7 +20397,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T366" t="inlineStr">
+      <c r="S366" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20459,7 +20444,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T367" t="inlineStr">
+      <c r="S367" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20506,7 +20491,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T368" t="inlineStr">
+      <c r="S368" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20553,7 +20538,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T369" t="inlineStr">
+      <c r="S369" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20600,7 +20585,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T370" t="inlineStr">
+      <c r="S370" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20647,7 +20632,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T371" t="inlineStr">
+      <c r="S371" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20694,7 +20679,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T372" t="inlineStr">
+      <c r="S372" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20741,7 +20726,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T373" t="inlineStr">
+      <c r="S373" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20788,7 +20773,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T374" t="inlineStr">
+      <c r="S374" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20840,7 +20825,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T375" t="inlineStr">
+      <c r="S375" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20887,7 +20872,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T376" t="inlineStr">
+      <c r="S376" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20934,7 +20919,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T377" t="inlineStr">
+      <c r="S377" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -20981,7 +20966,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T378" t="inlineStr">
+      <c r="S378" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21028,7 +21013,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T379" t="inlineStr">
+      <c r="S379" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21075,7 +21060,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T380" t="inlineStr">
+      <c r="S380" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21122,7 +21107,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T381" t="inlineStr">
+      <c r="S381" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21174,7 +21159,7 @@
           <t>Galilei' = Alessandro Galilei, architetto della facciata di San Giovanni in Laterano. Perifrasi per metonimia dell'autore.</t>
         </is>
       </c>
-      <c r="T382" t="inlineStr">
+      <c r="S382" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21221,7 +21206,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T383" t="inlineStr">
+      <c r="S383" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21268,7 +21253,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T384" t="inlineStr">
+      <c r="S384" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21315,7 +21300,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T385" t="inlineStr">
+      <c r="S385" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21362,7 +21347,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T386" t="inlineStr">
+      <c r="S386" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21409,7 +21394,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T387" t="inlineStr">
+      <c r="S387" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21456,7 +21441,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T388" t="inlineStr">
+      <c r="S388" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21503,7 +21488,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T389" t="inlineStr">
+      <c r="S389" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21550,7 +21535,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T390" t="inlineStr">
+      <c r="S390" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21597,7 +21582,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T391" t="inlineStr">
+      <c r="S391" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21644,7 +21629,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T392" t="inlineStr">
+      <c r="S392" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21696,7 +21681,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T393" t="inlineStr">
+      <c r="S393" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21743,7 +21728,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T394" t="inlineStr">
+      <c r="S394" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21790,7 +21775,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T395" t="inlineStr">
+      <c r="S395" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21837,7 +21822,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T396" t="inlineStr">
+      <c r="S396" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21884,7 +21869,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T397" t="inlineStr">
+      <c r="S397" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21931,7 +21916,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T398" t="inlineStr">
+      <c r="S398" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -21978,7 +21963,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T399" t="inlineStr">
+      <c r="S399" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22025,7 +22010,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T400" t="inlineStr">
+      <c r="S400" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22072,7 +22057,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T401" t="inlineStr">
+      <c r="S401" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22119,7 +22104,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T402" t="inlineStr">
+      <c r="S402" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22166,7 +22151,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T403" t="inlineStr">
+      <c r="S403" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22216,7 +22201,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T404" t="inlineStr">
+      <c r="S404" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22271,7 +22256,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T405" t="inlineStr">
+      <c r="S405" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22313,7 +22298,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T406" t="inlineStr">
+      <c r="S406" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22360,7 +22345,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T407" t="inlineStr">
+      <c r="S407" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22407,7 +22392,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T408" t="inlineStr">
+      <c r="S408" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22454,7 +22439,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T409" t="inlineStr">
+      <c r="S409" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22506,7 +22491,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T410" t="inlineStr">
+      <c r="S410" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22563,7 +22548,7 @@
           <t>La “collina molisana” è impiegata come sineddoche spaziale dell’origine sociale del personaggio; lo spazio non è diegeticamente attivo ma funziona come proiezione identitaria e culturale.</t>
         </is>
       </c>
-      <c r="T411" t="inlineStr">
+      <c r="S411" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22620,7 +22605,7 @@
           <t>Luogo generico</t>
         </is>
       </c>
-      <c r="T412" t="inlineStr">
+      <c r="S412" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22677,7 +22662,7 @@
           <t>Aggettivo che evoca lo spazio dei Colli Albani/Castelli Romani</t>
         </is>
       </c>
-      <c r="T413" t="inlineStr">
+      <c r="S413" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22734,7 +22719,7 @@
           <t>Aggettivo che evoca lo spazio di Tivoli</t>
         </is>
       </c>
-      <c r="T414" t="inlineStr">
+      <c r="S414" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22786,7 +22771,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T415" t="inlineStr">
+      <c r="S415" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22838,7 +22823,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T416" t="inlineStr">
+      <c r="S416" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22890,7 +22875,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T417" t="inlineStr">
+      <c r="S417" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22942,7 +22927,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T418" t="inlineStr">
+      <c r="S418" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -22994,7 +22979,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T419" t="inlineStr">
+      <c r="S419" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23041,7 +23026,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T420" t="inlineStr">
+      <c r="S420" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23093,7 +23078,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T421" t="inlineStr">
+      <c r="S421" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23150,7 +23135,7 @@
           <t>Monteleone, probabilmente Monteleone sabino, indicato come luogo d'origine d'una delle "nipotine" al servizio dei Balducci</t>
         </is>
       </c>
-      <c r="T422" t="inlineStr">
+      <c r="S422" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23212,7 +23197,7 @@
           <t>Anzio si collona nel territorio costiero del Castelli Romani</t>
         </is>
       </c>
-      <c r="T423" t="inlineStr">
+      <c r="S423" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23269,7 +23254,7 @@
           <t>Area paesaggistica vaga e analogica, delimitata dal Tevere e costruita per accumulo descrittivo (castelli, vigne, colli, monti, piane), contrapposta alla città di Roma; spazio percepito e mitizzato da Liliana Balducci. Il Tevere funziona come barriera idrografica e simbolica di separazione tra spazio urbano e spazio campestre, più che come luogo in sé.</t>
         </is>
       </c>
-      <c r="T424" t="inlineStr">
+      <c r="S424" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23321,7 +23306,7 @@
           <t>Tevere e Biferno sono impiegati come sineddoche spaziale dei tratti diatopici della lingua di Ingravallo</t>
         </is>
       </c>
-      <c r="T425" t="inlineStr">
+      <c r="S425" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23378,7 +23363,7 @@
           <t>2026-04-08 00:00:00</t>
         </is>
       </c>
-      <c r="T426" t="inlineStr">
+      <c r="S426" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23435,7 +23420,7 @@
           <t>2026-04-08 00:00:00</t>
         </is>
       </c>
-      <c r="T427" t="inlineStr">
+      <c r="S427" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23482,7 +23467,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T428" t="inlineStr">
+      <c r="S428" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23534,7 +23519,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T429" t="inlineStr">
+      <c r="S429" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23581,7 +23566,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T430" t="inlineStr">
+      <c r="S430" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23628,7 +23613,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T431" t="inlineStr">
+      <c r="S431" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23680,7 +23665,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T432" t="inlineStr">
+      <c r="S432" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23732,7 +23717,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T433" t="inlineStr">
+      <c r="S433" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23784,7 +23769,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T434" t="inlineStr">
+      <c r="S434" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23831,7 +23816,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T435" t="inlineStr">
+      <c r="S435" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23878,7 +23863,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T436" t="inlineStr">
+      <c r="S436" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23925,7 +23910,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T437" t="inlineStr">
+      <c r="S437" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -23972,7 +23957,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T438" t="inlineStr">
+      <c r="S438" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24019,7 +24004,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T439" t="inlineStr">
+      <c r="S439" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24066,7 +24051,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T440" t="inlineStr">
+      <c r="S440" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24113,7 +24098,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T441" t="inlineStr">
+      <c r="S441" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24160,7 +24145,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T442" t="inlineStr">
+      <c r="S442" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24207,7 +24192,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T443" t="inlineStr">
+      <c r="S443" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24254,7 +24239,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T444" t="inlineStr">
+      <c r="S444" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24301,7 +24286,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T445" t="inlineStr">
+      <c r="S445" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24348,7 +24333,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T446" t="inlineStr">
+      <c r="S446" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24395,7 +24380,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T447" t="inlineStr">
+      <c r="S447" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24442,7 +24427,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T448" t="inlineStr">
+      <c r="S448" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24489,7 +24474,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T449" t="inlineStr">
+      <c r="S449" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24536,7 +24521,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T450" t="inlineStr">
+      <c r="S450" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24583,7 +24568,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T451" t="inlineStr">
+      <c r="S451" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24630,7 +24615,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T452" t="inlineStr">
+      <c r="S452" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24677,7 +24662,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T453" t="inlineStr">
+      <c r="S453" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24724,7 +24709,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T454" t="inlineStr">
+      <c r="S454" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24771,7 +24756,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T455" t="inlineStr">
+      <c r="S455" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24818,7 +24803,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T456" t="inlineStr">
+      <c r="S456" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24865,7 +24850,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T457" t="inlineStr">
+      <c r="S457" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24912,7 +24897,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T458" t="inlineStr">
+      <c r="S458" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -24959,7 +24944,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T459" t="inlineStr">
+      <c r="S459" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25011,7 +24996,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T460" t="inlineStr">
+      <c r="S460" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25058,7 +25043,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T461" t="inlineStr">
+      <c r="S461" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25110,7 +25095,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T462" t="inlineStr">
+      <c r="S462" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25157,7 +25142,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T463" t="inlineStr">
+      <c r="S463" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25204,7 +25189,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T464" t="inlineStr">
+      <c r="S464" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25251,7 +25236,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T465" t="inlineStr">
+      <c r="S465" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25298,7 +25283,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T466" t="inlineStr">
+      <c r="S466" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25350,7 +25335,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T467" t="inlineStr">
+      <c r="S467" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25402,7 +25387,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T468" t="inlineStr">
+      <c r="S468" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25452,7 +25437,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T469" t="inlineStr">
+      <c r="S469" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25502,7 +25487,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T470" t="inlineStr">
+      <c r="S470" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25552,17 +25537,17 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>gaz_frattocchie|gaz_due_santi</t>
+        </is>
+      </c>
       <c r="R471" t="inlineStr">
         <is>
-          <t>gaz_frattocchie|gaz_due_santi</t>
+          <t>between</t>
         </is>
       </c>
       <c r="S471" t="inlineStr">
-        <is>
-          <t>between</t>
-        </is>
-      </c>
-      <c r="T471" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25627,7 +25612,7 @@
           <t>Possibile referente: Castello della Castelluccia, circa 41.7443, 12.6165</t>
         </is>
       </c>
-      <c r="T472" t="inlineStr">
+      <c r="S472" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25677,7 +25662,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T473" t="inlineStr">
+      <c r="S473" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25719,7 +25704,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T474" t="inlineStr">
+      <c r="S474" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25766,7 +25751,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T475" t="inlineStr">
+      <c r="S475" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25813,7 +25798,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T476" t="inlineStr">
+      <c r="S476" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25860,7 +25845,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T477" t="inlineStr">
+      <c r="S477" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25907,7 +25892,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T478" t="inlineStr">
+      <c r="S478" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -25959,7 +25944,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T479" t="inlineStr">
+      <c r="S479" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26009,7 +25994,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T480" t="inlineStr">
+      <c r="S480" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26064,7 +26049,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T481" t="inlineStr">
+      <c r="S481" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26114,7 +26099,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T482" t="inlineStr">
+      <c r="S482" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26164,7 +26149,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T483" t="inlineStr">
+      <c r="S483" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26206,7 +26191,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T484" t="inlineStr">
+      <c r="S484" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26258,7 +26243,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T485" t="inlineStr">
+      <c r="S485" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26305,7 +26290,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T486" t="inlineStr">
+      <c r="S486" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26352,7 +26337,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T487" t="inlineStr">
+      <c r="S487" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26402,7 +26387,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T488" t="inlineStr">
+      <c r="S488" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26452,7 +26437,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T489" t="inlineStr">
+      <c r="S489" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26502,7 +26487,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T490" t="inlineStr">
+      <c r="S490" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26552,7 +26537,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T491" t="inlineStr">
+      <c r="S491" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26602,7 +26587,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T492" t="inlineStr">
+      <c r="S492" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26644,7 +26629,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T493" t="inlineStr">
+      <c r="S493" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26694,7 +26679,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T494" t="inlineStr">
+      <c r="S494" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26744,7 +26729,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T495" t="inlineStr">
+      <c r="S495" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26794,7 +26779,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T496" t="inlineStr">
+      <c r="S496" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26844,7 +26829,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T497" t="inlineStr">
+      <c r="S497" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26894,7 +26879,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T498" t="inlineStr">
+      <c r="S498" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26936,7 +26921,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T499" t="inlineStr">
+      <c r="S499" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -26985,15 +26970,10 @@
       </c>
       <c r="P500" t="inlineStr">
         <is>
-          <t>Voce narrante distinta dal focalizzatore: la voce «tradisce l'incursione del narratore gaddiano» (Perosa 2023a, p. 238).</t>
-        </is>
-      </c>
-      <c r="Q500" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="T500" t="inlineStr">
+          <t>La critica vi osserva l’incursione del narratore gaddiano nello sguardo del personaggio (Perosa 2023a, p. 238).</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27042,15 +27022,10 @@
       </c>
       <c r="P501" t="inlineStr">
         <is>
-          <t>Voce narrante distinta dal focalizzatore: la voce «tradisce l'incursione del narratore gaddiano» (Perosa 2023a, p. 238).</t>
-        </is>
-      </c>
-      <c r="Q501" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="T501" t="inlineStr">
+          <t>La critica vi osserva l’incursione del narratore gaddiano nello sguardo del personaggio (Perosa 2023a, p. 238).</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27102,7 +27077,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T502" t="inlineStr">
+      <c r="S502" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27154,7 +27129,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T503" t="inlineStr">
+      <c r="S503" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27201,7 +27176,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T504" t="inlineStr">
+      <c r="S504" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27248,7 +27223,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T505" t="inlineStr">
+      <c r="S505" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27300,7 +27275,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T506" t="inlineStr">
+      <c r="S506" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27347,7 +27322,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T507" t="inlineStr">
+      <c r="S507" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27394,7 +27369,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T508" t="inlineStr">
+      <c r="S508" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27446,7 +27421,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T509" t="inlineStr">
+      <c r="S509" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27498,7 +27473,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T510" t="inlineStr">
+      <c r="S510" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27545,7 +27520,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T511" t="inlineStr">
+      <c r="S511" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27597,7 +27572,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T512" t="inlineStr">
+      <c r="S512" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27649,7 +27624,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T513" t="inlineStr">
+      <c r="S513" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27696,7 +27671,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T514" t="inlineStr">
+      <c r="S514" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27743,7 +27718,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T515" t="inlineStr">
+      <c r="S515" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27795,7 +27770,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T516" t="inlineStr">
+      <c r="S516" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27847,7 +27822,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T517" t="inlineStr">
+      <c r="S517" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27894,7 +27869,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T518" t="inlineStr">
+      <c r="S518" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27941,7 +27916,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T519" t="inlineStr">
+      <c r="S519" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -27988,7 +27963,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T520" t="inlineStr">
+      <c r="S520" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28035,7 +28010,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T521" t="inlineStr">
+      <c r="S521" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28082,7 +28057,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T522" t="inlineStr">
+      <c r="S522" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28129,7 +28104,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T523" t="inlineStr">
+      <c r="S523" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28181,7 +28156,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T524" t="inlineStr">
+      <c r="S524" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28233,7 +28208,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T525" t="inlineStr">
+      <c r="S525" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28280,7 +28255,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T526" t="inlineStr">
+      <c r="S526" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28327,7 +28302,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T527" t="inlineStr">
+      <c r="S527" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28374,7 +28349,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T528" t="inlineStr">
+      <c r="S528" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28421,7 +28396,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T529" t="inlineStr">
+      <c r="S529" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28468,7 +28443,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T530" t="inlineStr">
+      <c r="S530" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28515,7 +28490,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T531" t="inlineStr">
+      <c r="S531" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28562,7 +28537,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T532" t="inlineStr">
+      <c r="S532" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28609,7 +28584,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T533" t="inlineStr">
+      <c r="S533" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28656,7 +28631,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T534" t="inlineStr">
+      <c r="S534" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28706,7 +28681,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T535" t="inlineStr">
+      <c r="S535" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28756,7 +28731,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T536" t="inlineStr">
+      <c r="S536" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28806,7 +28781,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T537" t="inlineStr">
+      <c r="S537" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28856,7 +28831,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T538" t="inlineStr">
+      <c r="S538" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28898,7 +28873,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T539" t="inlineStr">
+      <c r="S539" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28945,7 +28920,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T540" t="inlineStr">
+      <c r="S540" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -28992,7 +28967,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T541" t="inlineStr">
+      <c r="S541" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29044,7 +29019,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T542" t="inlineStr">
+      <c r="S542" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29096,7 +29071,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T543" t="inlineStr">
+      <c r="S543" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29143,7 +29118,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T544" t="inlineStr">
+      <c r="S544" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29190,7 +29165,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T545" t="inlineStr">
+      <c r="S545" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29237,7 +29212,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T546" t="inlineStr">
+      <c r="S546" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29284,7 +29259,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T547" t="inlineStr">
+      <c r="S547" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29331,7 +29306,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T548" t="inlineStr">
+      <c r="S548" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29383,7 +29358,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T549" t="inlineStr">
+      <c r="S549" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -29435,7 +29410,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T550" t="inlineStr">
+      <c r="S550" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -29482,7 +29457,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T551" t="inlineStr">
+      <c r="S551" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29534,7 +29509,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T552" t="inlineStr">
+      <c r="S552" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29581,7 +29556,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T553" t="inlineStr">
+      <c r="S553" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29628,7 +29603,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T554" t="inlineStr">
+      <c r="S554" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29675,7 +29650,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T555" t="inlineStr">
+      <c r="S555" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29722,7 +29697,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T556" t="inlineStr">
+      <c r="S556" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29769,7 +29744,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T557" t="inlineStr">
+      <c r="S557" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29816,7 +29791,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T558" t="inlineStr">
+      <c r="S558" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29863,7 +29838,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T559" t="inlineStr">
+      <c r="S559" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29910,7 +29885,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T560" t="inlineStr">
+      <c r="S560" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -29957,7 +29932,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T561" t="inlineStr">
+      <c r="S561" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30004,7 +29979,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T562" t="inlineStr">
+      <c r="S562" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30056,7 +30031,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T563" t="inlineStr">
+      <c r="S563" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30108,7 +30083,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T564" t="inlineStr">
+      <c r="S564" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30155,7 +30130,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T565" t="inlineStr">
+      <c r="S565" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30202,7 +30177,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T566" t="inlineStr">
+      <c r="S566" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30249,7 +30224,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T567" t="inlineStr">
+      <c r="S567" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30296,7 +30271,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T568" t="inlineStr">
+      <c r="S568" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30343,7 +30318,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T569" t="inlineStr">
+      <c r="S569" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30390,7 +30365,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T570" t="inlineStr">
+      <c r="S570" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30437,7 +30412,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T571" t="inlineStr">
+      <c r="S571" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30484,7 +30459,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T572" t="inlineStr">
+      <c r="S572" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30531,7 +30506,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T573" t="inlineStr">
+      <c r="S573" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30578,7 +30553,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T574" t="inlineStr">
+      <c r="S574" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30630,7 +30605,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T575" t="inlineStr">
+      <c r="S575" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30677,7 +30652,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T576" t="inlineStr">
+      <c r="S576" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30724,7 +30699,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T577" t="inlineStr">
+      <c r="S577" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30776,7 +30751,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T578" t="inlineStr">
+      <c r="S578" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30823,7 +30798,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T579" t="inlineStr">
+      <c r="S579" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30870,7 +30845,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T580" t="inlineStr">
+      <c r="S580" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30922,17 +30897,17 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>gaz_san_carlo_alle_quattro_fontane</t>
+        </is>
+      </c>
       <c r="R581" t="inlineStr">
         <is>
-          <t>gaz_san_carlo_alle_quattro_fontane</t>
+          <t>adjacentto</t>
         </is>
       </c>
       <c r="S581" t="inlineStr">
-        <is>
-          <t>adjacentto</t>
-        </is>
-      </c>
-      <c r="T581" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -30979,7 +30954,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T582" t="inlineStr">
+      <c r="S582" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31031,7 +31006,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T583" t="inlineStr">
+      <c r="S583" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31078,7 +31053,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T584" t="inlineStr">
+      <c r="S584" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31125,7 +31100,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T585" t="inlineStr">
+      <c r="S585" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31172,7 +31147,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T586" t="inlineStr">
+      <c r="S586" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31219,7 +31194,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T587" t="inlineStr">
+      <c r="S587" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31266,7 +31241,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T588" t="inlineStr">
+      <c r="S588" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31313,7 +31288,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T589" t="inlineStr">
+      <c r="S589" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31360,7 +31335,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T590" t="inlineStr">
+      <c r="S590" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31407,7 +31382,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T591" t="inlineStr">
+      <c r="S591" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31454,7 +31429,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T592" t="inlineStr">
+      <c r="S592" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31506,7 +31481,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T593" t="inlineStr">
+      <c r="S593" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31553,7 +31528,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T594" t="inlineStr">
+      <c r="S594" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31600,7 +31575,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T595" t="inlineStr">
+      <c r="S595" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31647,7 +31622,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T596" t="inlineStr">
+      <c r="S596" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31694,7 +31669,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T597" t="inlineStr">
+      <c r="S597" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31741,7 +31716,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T598" t="inlineStr">
+      <c r="S598" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31796,7 +31771,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T599" t="inlineStr">
+      <c r="S599" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31851,7 +31826,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T600" t="inlineStr">
+      <c r="S600" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31893,7 +31868,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T601" t="inlineStr">
+      <c r="S601" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31940,7 +31915,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T602" t="inlineStr">
+      <c r="S602" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -31987,7 +31962,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T603" t="inlineStr">
+      <c r="S603" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32039,7 +32014,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T604" t="inlineStr">
+      <c r="S604" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32091,7 +32066,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T605" t="inlineStr">
+      <c r="S605" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32138,7 +32113,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T606" t="inlineStr">
+      <c r="S606" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32190,7 +32165,7 @@
           <t>Giorgio Pinotti identifica esplicitamente la sequenza: «è stata Clelia Farcioni a fare la spia col maresciallo Santarella» nell’incontro di Santa Margherita in Abitacolo. Giorgio Pinotti, “Liliana Balducci e il suo boja?”, (Edinburgh Journal of Gadda Studies)</t>
         </is>
       </c>
-      <c r="T607" t="inlineStr">
+      <c r="S607" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32242,7 +32217,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T608" t="inlineStr">
+      <c r="S608" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32294,7 +32269,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T609" t="inlineStr">
+      <c r="S609" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32346,7 +32321,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T610" t="inlineStr">
+      <c r="S610" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32398,7 +32373,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T611" t="inlineStr">
+      <c r="S611" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32450,7 +32425,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T612" t="inlineStr">
+      <c r="S612" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32505,7 +32480,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T613" t="inlineStr">
+      <c r="S613" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32560,7 +32535,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T614" t="inlineStr">
+      <c r="S614" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32615,7 +32590,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T615" t="inlineStr">
+      <c r="S615" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32680,7 +32655,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T616" t="inlineStr">
+      <c r="S616" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32740,7 +32715,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T617" t="inlineStr">
+      <c r="S617" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32800,7 +32775,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T618" t="inlineStr">
+      <c r="S618" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32847,7 +32822,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T619" t="inlineStr">
+      <c r="S619" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32894,7 +32869,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T620" t="inlineStr">
+      <c r="S620" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32941,7 +32916,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T621" t="inlineStr">
+      <c r="S621" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -32988,7 +32963,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T622" t="inlineStr">
+      <c r="S622" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33035,7 +33010,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T623" t="inlineStr">
+      <c r="S623" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33082,7 +33057,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T624" t="inlineStr">
+      <c r="S624" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33139,7 +33114,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T625" t="inlineStr">
+      <c r="S625" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33186,7 +33161,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T626" t="inlineStr">
+      <c r="S626" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33233,7 +33208,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T627" t="inlineStr">
+      <c r="S627" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33285,7 +33260,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T628" t="inlineStr">
+      <c r="S628" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33337,7 +33312,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T629" t="inlineStr">
+      <c r="S629" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33394,7 +33369,7 @@
 Manzotti ricava l’identificazione dalla guida del Touring Italia centrale I, p. 561, una delle fonti topografiche impiegate da Gadda. Emilio Manzotti, «Era l’alba, e più», nota al rigo 135 (EJGS)</t>
         </is>
       </c>
-      <c r="T630" t="inlineStr">
+      <c r="S630" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33444,7 +33419,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T631" t="inlineStr">
+      <c r="S631" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33493,15 +33468,10 @@
       </c>
       <c r="P632" t="inlineStr">
         <is>
-          <t>Voce narrante distinta dal focalizzatore: «divaricazione tra voce e punto di vista» (Savettieri 2020, p. 44).</t>
-        </is>
-      </c>
-      <c r="Q632" t="inlineStr">
-        <is>
-          <t>narrator</t>
-        </is>
-      </c>
-      <c r="T632" t="inlineStr">
+          <t>La critica vi osserva una divaricazione tra voce e punto di vista (Savettieri 2020, p. 44).</t>
+        </is>
+      </c>
+      <c r="S632" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33553,7 +33523,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T633" t="inlineStr">
+      <c r="S633" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33600,7 +33570,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T634" t="inlineStr">
+      <c r="S634" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33647,7 +33617,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T635" t="inlineStr">
+      <c r="S635" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33694,7 +33664,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T636" t="inlineStr">
+      <c r="S636" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33759,7 +33729,7 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QPa 212, percorso sognato (Pestalozzi): Manzotti (p. 269) legge «per fil a dest» come un cambio di direzione perpendicolare, in realtà verso sinistra (a sud, verso il Circeo); lettura attribuita, fase 3.</t>
         </is>
       </c>
-      <c r="T637" t="inlineStr">
+      <c r="S637" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33819,7 +33789,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T638" t="inlineStr">
+      <c r="S638" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33879,7 +33849,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T639" t="inlineStr">
+      <c r="S639" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33926,7 +33896,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T640" t="inlineStr">
+      <c r="S640" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -33978,7 +33948,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T641" t="inlineStr">
+      <c r="S641" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34030,7 +34000,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T642" t="inlineStr">
+      <c r="S642" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34077,7 +34047,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T643" t="inlineStr">
+      <c r="S643" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34124,7 +34094,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T644" t="inlineStr">
+      <c r="S644" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34171,7 +34141,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T645" t="inlineStr">
+      <c r="S645" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34218,7 +34188,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T646" t="inlineStr">
+      <c r="S646" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34268,7 +34238,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T647" t="inlineStr">
+      <c r="S647" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34318,7 +34288,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T648" t="inlineStr">
+      <c r="S648" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34360,7 +34330,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T649" t="inlineStr">
+      <c r="S649" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34402,7 +34372,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T650" t="inlineStr">
+      <c r="S650" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34449,7 +34419,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T651" t="inlineStr">
+      <c r="S651" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34496,7 +34466,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T652" t="inlineStr">
+      <c r="S652" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34548,7 +34518,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T653" t="inlineStr">
+      <c r="S653" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34595,7 +34565,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T654" t="inlineStr">
+      <c r="S654" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34642,7 +34612,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T655" t="inlineStr">
+      <c r="S655" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34694,17 +34664,17 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
+      <c r="Q656" t="inlineStr">
+        <is>
+          <t>orto_vigna_due_santi</t>
+        </is>
+      </c>
       <c r="R656" t="inlineStr">
         <is>
-          <t>orto_vigna_due_santi</t>
+          <t>adjacentto</t>
         </is>
       </c>
       <c r="S656" t="inlineStr">
-        <is>
-          <t>adjacentto</t>
-        </is>
-      </c>
-      <c r="T656" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34751,7 +34721,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T657" t="inlineStr">
+      <c r="S657" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34798,7 +34768,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T658" t="inlineStr">
+      <c r="S658" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34850,7 +34820,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T659" t="inlineStr">
+      <c r="S659" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34902,7 +34872,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T660" t="inlineStr">
+      <c r="S660" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -34949,7 +34919,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T661" t="inlineStr">
+      <c r="S661" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35006,7 +34976,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T662" t="inlineStr">
+      <c r="S662" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35053,7 +35023,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T663" t="inlineStr">
+      <c r="S663" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35105,7 +35075,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T664" t="inlineStr">
+      <c r="S664" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35157,7 +35127,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T665" t="inlineStr">
+      <c r="S665" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35209,7 +35179,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T666" t="inlineStr">
+      <c r="S666" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35256,7 +35226,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T667" t="inlineStr">
+      <c r="S667" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35303,7 +35273,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T668" t="inlineStr">
+      <c r="S668" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35350,7 +35320,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T669" t="inlineStr">
+      <c r="S669" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35397,7 +35367,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T670" t="inlineStr">
+      <c r="S670" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35449,7 +35419,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T671" t="inlineStr">
+      <c r="S671" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35501,7 +35471,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T672" t="inlineStr">
+      <c r="S672" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35548,7 +35518,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T673" t="inlineStr">
+      <c r="S673" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35600,7 +35570,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T674" t="inlineStr">
+      <c r="S674" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35660,7 +35630,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T675" t="inlineStr">
+      <c r="S675" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35720,7 +35690,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T676" t="inlineStr">
+      <c r="S676" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35785,17 +35755,17 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
+      <c r="Q677" t="inlineStr">
+        <is>
+          <t>gaz_castel_di_leva|gaz_ponte_divino_amore</t>
+        </is>
+      </c>
       <c r="R677" t="inlineStr">
         <is>
-          <t>gaz_castel_di_leva|gaz_ponte_divino_amore</t>
+          <t>near</t>
         </is>
       </c>
       <c r="S677" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="T677" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35842,7 +35812,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T678" t="inlineStr">
+      <c r="S678" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35889,7 +35859,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T679" t="inlineStr">
+      <c r="S679" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35936,7 +35906,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T680" t="inlineStr">
+      <c r="S680" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -35983,7 +35953,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T681" t="inlineStr">
+      <c r="S681" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36030,7 +36000,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T682" t="inlineStr">
+      <c r="S682" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36077,7 +36047,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T683" t="inlineStr">
+      <c r="S683" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36127,7 +36097,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T684" t="inlineStr">
+      <c r="S684" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36177,7 +36147,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T685" t="inlineStr">
+      <c r="S685" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36227,7 +36197,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T686" t="inlineStr">
+      <c r="S686" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36277,7 +36247,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T687" t="inlineStr">
+      <c r="S687" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36327,7 +36297,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T688" t="inlineStr">
+      <c r="S688" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36377,7 +36347,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T689" t="inlineStr">
+      <c r="S689" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36419,7 +36389,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T690" t="inlineStr">
+      <c r="S690" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36461,7 +36431,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T691" t="inlineStr">
+      <c r="S691" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36503,7 +36473,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T692" t="inlineStr">
+      <c r="S692" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36550,7 +36520,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T693" t="inlineStr">
+      <c r="S693" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36602,7 +36572,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T694" t="inlineStr">
+      <c r="S694" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36654,12 +36624,12 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="R695" t="inlineStr">
+      <c r="Q695" t="inlineStr">
         <is>
           <t>near:gaz_ponte_divino_amore|above:gaz_ferrovia_roma_velletri</t>
         </is>
       </c>
-      <c r="T695" t="inlineStr">
+      <c r="S695" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36706,7 +36676,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T696" t="inlineStr">
+      <c r="S696" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36753,7 +36723,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T697" t="inlineStr">
+      <c r="S697" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36800,7 +36770,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T698" t="inlineStr">
+      <c r="S698" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36852,7 +36822,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T699" t="inlineStr">
+      <c r="S699" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36899,7 +36869,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T700" t="inlineStr">
+      <c r="S700" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36946,7 +36916,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T701" t="inlineStr">
+      <c r="S701" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -36993,7 +36963,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T702" t="inlineStr">
+      <c r="S702" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37045,17 +37015,17 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
+      <c r="Q703" t="inlineStr">
+        <is>
+          <t>gaz_via_della_falcognana|gaz_ponte_divino_amore|gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="R703" t="inlineStr">
         <is>
-          <t>gaz_via_della_falcognana|gaz_ponte_divino_amore|gaz_ferrovia_roma_velletri</t>
+          <t>near</t>
         </is>
       </c>
       <c r="S703" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="T703" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37107,7 +37077,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T704" t="inlineStr">
+      <c r="S704" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37159,7 +37129,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T705" t="inlineStr">
+      <c r="S705" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37201,7 +37171,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T706" t="inlineStr">
+      <c r="S706" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37248,7 +37218,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T707" t="inlineStr">
+      <c r="S707" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37300,7 +37270,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T708" t="inlineStr">
+      <c r="S708" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37352,7 +37322,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T709" t="inlineStr">
+      <c r="S709" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37404,7 +37374,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T710" t="inlineStr">
+      <c r="S710" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37456,7 +37426,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T711" t="inlineStr">
+      <c r="S711" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37508,7 +37478,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T712" t="inlineStr">
+      <c r="S712" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37560,7 +37530,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T713" t="inlineStr">
+      <c r="S713" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37607,7 +37577,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T714" t="inlineStr">
+      <c r="S714" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37654,7 +37624,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T715" t="inlineStr">
+      <c r="S715" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37706,7 +37676,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T716" t="inlineStr">
+      <c r="S716" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37758,7 +37728,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T717" t="inlineStr">
+      <c r="S717" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37805,7 +37775,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T718" t="inlineStr">
+      <c r="S718" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37852,7 +37822,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T719" t="inlineStr">
+      <c r="S719" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37899,7 +37869,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T720" t="inlineStr">
+      <c r="S720" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -37951,7 +37921,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T721" t="inlineStr">
+      <c r="S721" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38003,7 +37973,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T722" t="inlineStr">
+      <c r="S722" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38055,7 +38025,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T723" t="inlineStr">
+      <c r="S723" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38102,7 +38072,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T724" t="inlineStr">
+      <c r="S724" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38149,7 +38119,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T725" t="inlineStr">
+      <c r="S725" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38196,7 +38166,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T726" t="inlineStr">
+      <c r="S726" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38243,7 +38213,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T727" t="inlineStr">
+      <c r="S727" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38295,7 +38265,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T728" t="inlineStr">
+      <c r="S728" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38342,7 +38312,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T729" t="inlineStr">
+      <c r="S729" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38389,7 +38359,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T730" t="inlineStr">
+      <c r="S730" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38436,7 +38406,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T731" t="inlineStr">
+      <c r="S731" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38488,7 +38458,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T732" t="inlineStr">
+      <c r="S732" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38540,7 +38510,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T733" t="inlineStr">
+      <c r="S733" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38592,7 +38562,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T734" t="inlineStr">
+      <c r="S734" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38639,7 +38609,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T735" t="inlineStr">
+      <c r="S735" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38686,7 +38656,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T736" t="inlineStr">
+      <c r="S736" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38733,7 +38703,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T737" t="inlineStr">
+      <c r="S737" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38785,7 +38755,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T738" t="inlineStr">
+      <c r="S738" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38837,7 +38807,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T739" t="inlineStr">
+      <c r="S739" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38889,7 +38859,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T740" t="inlineStr">
+      <c r="S740" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38941,7 +38911,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T741" t="inlineStr">
+      <c r="S741" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -38993,7 +38963,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T742" t="inlineStr">
+      <c r="S742" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39045,7 +39015,7 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
-      <c r="T743" t="inlineStr">
+      <c r="S743" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39092,7 +39062,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T744" t="inlineStr">
+      <c r="S744" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39144,7 +39114,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T745" t="inlineStr">
+      <c r="S745" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39196,7 +39166,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T746" t="inlineStr">
+      <c r="S746" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39248,7 +39218,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T747" t="inlineStr">
+      <c r="S747" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39300,7 +39270,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T748" t="inlineStr">
+      <c r="S748" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39347,7 +39317,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T749" t="inlineStr">
+      <c r="S749" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39399,7 +39369,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T750" t="inlineStr">
+      <c r="S750" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39451,7 +39421,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T751" t="inlineStr">
+      <c r="S751" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39498,7 +39468,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T752" t="inlineStr">
+      <c r="S752" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39545,7 +39515,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T753" t="inlineStr">
+      <c r="S753" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39597,7 +39567,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T754" t="inlineStr">
+      <c r="S754" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39649,7 +39619,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T755" t="inlineStr">
+      <c r="S755" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39701,7 +39671,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T756" t="inlineStr">
+      <c r="S756" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39748,7 +39718,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T757" t="inlineStr">
+      <c r="S757" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39795,7 +39765,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T758" t="inlineStr">
+      <c r="S758" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39842,7 +39812,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T759" t="inlineStr">
+      <c r="S759" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39889,7 +39859,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T760" t="inlineStr">
+      <c r="S760" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39936,7 +39906,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T761" t="inlineStr">
+      <c r="S761" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -39983,7 +39953,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T762" t="inlineStr">
+      <c r="S762" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40030,7 +40000,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T763" t="inlineStr">
+      <c r="S763" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40077,7 +40047,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T764" t="inlineStr">
+      <c r="S764" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40124,7 +40094,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T765" t="inlineStr">
+      <c r="S765" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40171,7 +40141,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T766" t="inlineStr">
+      <c r="S766" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40218,7 +40188,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T767" t="inlineStr">
+      <c r="S767" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40265,7 +40235,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T768" t="inlineStr">
+      <c r="S768" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40317,7 +40287,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T769" t="inlineStr">
+      <c r="S769" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40369,17 +40339,17 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
+      <c r="Q770" t="inlineStr">
+        <is>
+          <t>gaz_via_ardeatina</t>
+        </is>
+      </c>
       <c r="R770" t="inlineStr">
         <is>
-          <t>gaz_via_ardeatina</t>
+          <t>near</t>
         </is>
       </c>
       <c r="S770" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="T770" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40426,7 +40396,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T771" t="inlineStr">
+      <c r="S771" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40473,7 +40443,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T772" t="inlineStr">
+      <c r="S772" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40520,7 +40490,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T773" t="inlineStr">
+      <c r="S773" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40567,7 +40537,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T774" t="inlineStr">
+      <c r="S774" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40614,7 +40584,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T775" t="inlineStr">
+      <c r="S775" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40661,7 +40631,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T776" t="inlineStr">
+      <c r="S776" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40708,7 +40678,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T777" t="inlineStr">
+      <c r="S777" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40755,7 +40725,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T778" t="inlineStr">
+      <c r="S778" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40802,7 +40772,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T779" t="inlineStr">
+      <c r="S779" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40849,7 +40819,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T780" t="inlineStr">
+      <c r="S780" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40896,7 +40866,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T781" t="inlineStr">
+      <c r="S781" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40943,7 +40913,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T782" t="inlineStr">
+      <c r="S782" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -40995,7 +40965,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T783" t="inlineStr">
+      <c r="S783" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41047,7 +41017,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T784" t="inlineStr">
+      <c r="S784" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41099,7 +41069,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T785" t="inlineStr">
+      <c r="S785" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41146,7 +41116,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T786" t="inlineStr">
+      <c r="S786" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41193,7 +41163,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T787" t="inlineStr">
+      <c r="S787" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41243,7 +41213,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T788" t="inlineStr">
+      <c r="S788" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41293,7 +41263,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T789" t="inlineStr">
+      <c r="S789" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41335,7 +41305,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T790" t="inlineStr">
+      <c r="S790" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41382,7 +41352,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T791" t="inlineStr">
+      <c r="S791" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41429,7 +41399,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T792" t="inlineStr">
+      <c r="S792" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41471,7 +41441,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T793" t="inlineStr">
+      <c r="S793" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41513,7 +41483,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T794" t="inlineStr">
+      <c r="S794" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41560,7 +41530,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T795" t="inlineStr">
+      <c r="S795" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41607,7 +41577,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T796" t="inlineStr">
+      <c r="S796" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41654,7 +41624,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T797" t="inlineStr">
+      <c r="S797" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41701,7 +41671,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T798" t="inlineStr">
+      <c r="S798" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41748,7 +41718,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T799" t="inlineStr">
+      <c r="S799" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41795,7 +41765,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T800" t="inlineStr">
+      <c r="S800" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41842,7 +41812,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T801" t="inlineStr">
+      <c r="S801" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41889,7 +41859,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T802" t="inlineStr">
+      <c r="S802" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41936,7 +41906,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T803" t="inlineStr">
+      <c r="S803" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -41983,7 +41953,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T804" t="inlineStr">
+      <c r="S804" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42030,7 +42000,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T805" t="inlineStr">
+      <c r="S805" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42077,7 +42047,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T806" t="inlineStr">
+      <c r="S806" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42124,7 +42094,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T807" t="inlineStr">
+      <c r="S807" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42171,7 +42141,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T808" t="inlineStr">
+      <c r="S808" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42218,7 +42188,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T809" t="inlineStr">
+      <c r="S809" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42265,7 +42235,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T810" t="inlineStr">
+      <c r="S810" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42312,7 +42282,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T811" t="inlineStr">
+      <c r="S811" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42359,7 +42329,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T812" t="inlineStr">
+      <c r="S812" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42406,7 +42376,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T813" t="inlineStr">
+      <c r="S813" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42453,7 +42423,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T814" t="inlineStr">
+      <c r="S814" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42500,7 +42470,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T815" t="inlineStr">
+      <c r="S815" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42547,7 +42517,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T816" t="inlineStr">
+      <c r="S816" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42594,7 +42564,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T817" t="inlineStr">
+      <c r="S817" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42641,7 +42611,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T818" t="inlineStr">
+      <c r="S818" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42688,7 +42658,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T819" t="inlineStr">
+      <c r="S819" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42735,7 +42705,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T820" t="inlineStr">
+      <c r="S820" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42782,7 +42752,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T821" t="inlineStr">
+      <c r="S821" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42829,7 +42799,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T822" t="inlineStr">
+      <c r="S822" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42876,7 +42846,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T823" t="inlineStr">
+      <c r="S823" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42923,7 +42893,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T824" t="inlineStr">
+      <c r="S824" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -42970,7 +42940,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T825" t="inlineStr">
+      <c r="S825" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43017,7 +42987,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T826" t="inlineStr">
+      <c r="S826" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43064,7 +43034,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T827" t="inlineStr">
+      <c r="S827" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43111,7 +43081,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T828" t="inlineStr">
+      <c r="S828" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43158,7 +43128,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T829" t="inlineStr">
+      <c r="S829" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43210,7 +43180,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T830" t="inlineStr">
+      <c r="S830" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -43257,7 +43227,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T831" t="inlineStr">
+      <c r="S831" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43304,7 +43274,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T832" t="inlineStr">
+      <c r="S832" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43351,7 +43321,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T833" t="inlineStr">
+      <c r="S833" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43398,7 +43368,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T834" t="inlineStr">
+      <c r="S834" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43445,7 +43415,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T835" t="inlineStr">
+      <c r="S835" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43495,7 +43465,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T836" t="inlineStr">
+      <c r="S836" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43545,7 +43515,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T837" t="inlineStr">
+      <c r="S837" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43595,7 +43565,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T838" t="inlineStr">
+      <c r="S838" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43645,7 +43615,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T839" t="inlineStr">
+      <c r="S839" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43695,7 +43665,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T840" t="inlineStr">
+      <c r="S840" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43745,7 +43715,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T841" t="inlineStr">
+      <c r="S841" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43795,7 +43765,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T842" t="inlineStr">
+      <c r="S842" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43845,7 +43815,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T843" t="inlineStr">
+      <c r="S843" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43895,7 +43865,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T844" t="inlineStr">
+      <c r="S844" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43937,7 +43907,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T845" t="inlineStr">
+      <c r="S845" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -43979,7 +43949,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T846" t="inlineStr">
+      <c r="S846" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44021,7 +43991,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T847" t="inlineStr">
+      <c r="S847" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44068,7 +44038,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T848" t="inlineStr">
+      <c r="S848" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44115,7 +44085,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T849" t="inlineStr">
+      <c r="S849" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44162,7 +44132,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T850" t="inlineStr">
+      <c r="S850" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44209,7 +44179,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T851" t="inlineStr">
+      <c r="S851" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44261,7 +44231,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T852" t="inlineStr">
+      <c r="S852" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44313,7 +44283,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T853" t="inlineStr">
+      <c r="S853" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44365,7 +44335,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T854" t="inlineStr">
+      <c r="S854" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44412,7 +44382,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T855" t="inlineStr">
+      <c r="S855" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44459,7 +44429,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T856" t="inlineStr">
+      <c r="S856" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44506,7 +44476,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T857" t="inlineStr">
+      <c r="S857" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44553,7 +44523,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T858" t="inlineStr">
+      <c r="S858" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44605,7 +44575,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T859" t="inlineStr">
+      <c r="S859" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44652,7 +44622,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T860" t="inlineStr">
+      <c r="S860" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44699,7 +44669,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T861" t="inlineStr">
+      <c r="S861" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44746,7 +44716,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T862" t="inlineStr">
+      <c r="S862" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44793,7 +44763,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T863" t="inlineStr">
+      <c r="S863" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44843,7 +44813,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T864" t="inlineStr">
+      <c r="S864" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44893,7 +44863,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T865" t="inlineStr">
+      <c r="S865" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44943,7 +44913,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T866" t="inlineStr">
+      <c r="S866" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -44993,7 +44963,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T867" t="inlineStr">
+      <c r="S867" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45043,7 +45013,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T868" t="inlineStr">
+      <c r="S868" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45093,7 +45063,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T869" t="inlineStr">
+      <c r="S869" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45143,7 +45113,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T870" t="inlineStr">
+      <c r="S870" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45193,7 +45163,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T871" t="inlineStr">
+      <c r="S871" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45243,7 +45213,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T872" t="inlineStr">
+      <c r="S872" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45293,7 +45263,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T873" t="inlineStr">
+      <c r="S873" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45343,7 +45313,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T874" t="inlineStr">
+      <c r="S874" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45393,7 +45363,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T875" t="inlineStr">
+      <c r="S875" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45443,7 +45413,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T876" t="inlineStr">
+      <c r="S876" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45493,7 +45463,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T877" t="inlineStr">
+      <c r="S877" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45543,7 +45513,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T878" t="inlineStr">
+      <c r="S878" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45593,7 +45563,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T879" t="inlineStr">
+      <c r="S879" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45643,7 +45613,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T880" t="inlineStr">
+      <c r="S880" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45693,7 +45663,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T881" t="inlineStr">
+      <c r="S881" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45743,7 +45713,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T882" t="inlineStr">
+      <c r="S882" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45793,7 +45763,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T883" t="inlineStr">
+      <c r="S883" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45848,7 +45818,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T884" t="inlineStr">
+      <c r="S884" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45903,7 +45873,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T885" t="inlineStr">
+      <c r="S885" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -45958,7 +45928,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T886" t="inlineStr">
+      <c r="S886" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46013,7 +45983,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T887" t="inlineStr">
+      <c r="S887" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46068,7 +46038,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T888" t="inlineStr">
+      <c r="S888" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46123,7 +46093,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T889" t="inlineStr">
+      <c r="S889" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46178,7 +46148,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T890" t="inlineStr">
+      <c r="S890" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46233,7 +46203,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T891" t="inlineStr">
+      <c r="S891" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46288,17 +46258,17 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QPa 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
+      <c r="Q892" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="R892" t="inlineStr">
         <is>
-          <t>gaz_ferrovia_roma_velletri</t>
+          <t>near</t>
         </is>
       </c>
       <c r="S892" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="T892" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46353,17 +46323,17 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QPa 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
+      <c r="Q893" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="R893" t="inlineStr">
         <is>
-          <t>gaz_ferrovia_roma_velletri</t>
+          <t>near</t>
         </is>
       </c>
       <c r="S893" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="T893" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46418,17 +46388,17 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QPa 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
+      <c r="Q894" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="R894" t="inlineStr">
         <is>
-          <t>gaz_ferrovia_roma_velletri</t>
+          <t>near</t>
         </is>
       </c>
       <c r="S894" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="T894" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46483,17 +46453,17 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita). QPa 297: il passo dispone intorno al casale anche il ponte di Santa Fumia e Tor di Gheppio (luoghi narrativi, non ancore geografiche: relazione fra luoghi narrativi da modellare in T-47/T-53) e il passaggio a livello sulla ferrovia di Velletri «due chilometri più a nord» del Divino Amore.</t>
         </is>
       </c>
+      <c r="Q895" t="inlineStr">
+        <is>
+          <t>gaz_ferrovia_roma_velletri</t>
+        </is>
+      </c>
       <c r="R895" t="inlineStr">
         <is>
-          <t>gaz_ferrovia_roma_velletri</t>
+          <t>near</t>
         </is>
       </c>
       <c r="S895" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="T895" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46543,7 +46513,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T896" t="inlineStr">
+      <c r="S896" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46593,7 +46563,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T897" t="inlineStr">
+      <c r="S897" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46643,7 +46613,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T898" t="inlineStr">
+      <c r="S898" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46693,7 +46663,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T899" t="inlineStr">
+      <c r="S899" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46743,7 +46713,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T900" t="inlineStr">
+      <c r="S900" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46793,7 +46763,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T901" t="inlineStr">
+      <c r="S901" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46843,7 +46813,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T902" t="inlineStr">
+      <c r="S902" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46893,7 +46863,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T903" t="inlineStr">
+      <c r="S903" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46935,7 +46905,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T904" t="inlineStr">
+      <c r="S904" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -46977,7 +46947,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T905" t="inlineStr">
+      <c r="S905" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47019,7 +46989,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T906" t="inlineStr">
+      <c r="S906" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47061,7 +47031,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T907" t="inlineStr">
+      <c r="S907" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47113,7 +47083,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T908" t="inlineStr">
+      <c r="S908" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47160,7 +47130,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T909" t="inlineStr">
+      <c r="S909" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47207,7 +47177,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T910" t="inlineStr">
+      <c r="S910" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47254,7 +47224,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T911" t="inlineStr">
+      <c r="S911" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47306,7 +47276,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T912" t="inlineStr">
+      <c r="S912" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47358,7 +47328,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T913" t="inlineStr">
+      <c r="S913" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47405,7 +47375,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T914" t="inlineStr">
+      <c r="S914" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47452,7 +47422,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T915" t="inlineStr">
+      <c r="S915" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47504,7 +47474,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T916" t="inlineStr">
+      <c r="S916" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47556,7 +47526,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T917" t="inlineStr">
+      <c r="S917" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47603,7 +47573,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T918" t="inlineStr">
+      <c r="S918" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47650,7 +47620,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T919" t="inlineStr">
+      <c r="S919" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47702,17 +47672,17 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
+      <c r="Q920" t="inlineStr">
+        <is>
+          <t>gaz_via_ardeatina|gaz_santa_palomba</t>
+        </is>
+      </c>
       <c r="R920" t="inlineStr">
         <is>
-          <t>gaz_via_ardeatina|gaz_santa_palomba</t>
+          <t>near</t>
         </is>
       </c>
       <c r="S920" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="T920" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47764,17 +47734,17 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
+      <c r="Q921" t="inlineStr">
+        <is>
+          <t>gaz_via_ardeatina|gaz_santa_palomba</t>
+        </is>
+      </c>
       <c r="R921" t="inlineStr">
         <is>
-          <t>gaz_via_ardeatina|gaz_santa_palomba</t>
+          <t>near</t>
         </is>
       </c>
       <c r="S921" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="T921" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47821,7 +47791,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T922" t="inlineStr">
+      <c r="S922" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47868,7 +47838,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T923" t="inlineStr">
+      <c r="S923" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47915,7 +47885,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T924" t="inlineStr">
+      <c r="S924" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -47962,7 +47932,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T925" t="inlineStr">
+      <c r="S925" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48009,7 +47979,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T926" t="inlineStr">
+      <c r="S926" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48056,7 +48026,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T927" t="inlineStr">
+      <c r="S927" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48103,7 +48073,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T928" t="inlineStr">
+      <c r="S928" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48150,7 +48120,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T929" t="inlineStr">
+      <c r="S929" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48197,7 +48167,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T930" t="inlineStr">
+      <c r="S930" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48244,7 +48214,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T931" t="inlineStr">
+      <c r="S931" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48291,7 +48261,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T932" t="inlineStr">
+      <c r="S932" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48338,7 +48308,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T933" t="inlineStr">
+      <c r="S933" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48385,7 +48355,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T934" t="inlineStr">
+      <c r="S934" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48432,7 +48402,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T935" t="inlineStr">
+      <c r="S935" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48479,7 +48449,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T936" t="inlineStr">
+      <c r="S936" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48526,7 +48496,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T937" t="inlineStr">
+      <c r="S937" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48578,17 +48548,17 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
+      <c r="Q938" t="inlineStr">
+        <is>
+          <t>gaz_via_ardeatina|gaz_santa_palomba</t>
+        </is>
+      </c>
       <c r="R938" t="inlineStr">
         <is>
-          <t>gaz_via_ardeatina|gaz_santa_palomba</t>
+          <t>near</t>
         </is>
       </c>
       <c r="S938" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="T938" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48640,17 +48610,17 @@
           <t>Ancora: gaz_casale_abbruciato, nella posizione TCI adottata (Manzotti 2010, Tav. VI); posizione alternativa IGM a ovest della Roma–Napoli (Tav. VII), in discrepanza con il testo. Manzotti (2010, p. 269): la topografia di Gadda «pare combinare e forse confondere» le due ferrovie, «fondandosi […] più sulla memoria di escursioni in loco, che sui rilievi delle carte»: il testo prevale, la discrepanza non si corregge. Le altre ancore sono i luoghi che il passo dispone intorno al casale (relazione near, da rimodellare come ancoraggio relazionale, T-47). Pavona e Santa Maria delle Mole non sono nel testo: sono un'inferenza di Manzotti dai km 17,55 e 23,38 della Roma–Velletri (fase 3, lettura attribuita).</t>
         </is>
       </c>
+      <c r="Q939" t="inlineStr">
+        <is>
+          <t>gaz_via_ardeatina|gaz_santa_palomba</t>
+        </is>
+      </c>
       <c r="R939" t="inlineStr">
         <is>
-          <t>gaz_via_ardeatina|gaz_santa_palomba</t>
+          <t>near</t>
         </is>
       </c>
       <c r="S939" t="inlineStr">
-        <is>
-          <t>near</t>
-        </is>
-      </c>
-      <c r="T939" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48702,7 +48672,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T940" t="inlineStr">
+      <c r="S940" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48754,7 +48724,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T941" t="inlineStr">
+      <c r="S941" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48796,7 +48766,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T942" t="inlineStr">
+      <c r="S942" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48838,7 +48808,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T943" t="inlineStr">
+      <c r="S943" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48880,7 +48850,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T944" t="inlineStr">
+      <c r="S944" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48922,7 +48892,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T945" t="inlineStr">
+      <c r="S945" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -48964,7 +48934,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T946" t="inlineStr">
+      <c r="S946" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49016,7 +48986,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T947" t="inlineStr">
+      <c r="S947" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49058,7 +49028,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T948" t="inlineStr">
+      <c r="S948" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49100,7 +49070,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T949" t="inlineStr">
+      <c r="S949" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49142,7 +49112,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T950" t="inlineStr">
+      <c r="S950" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49194,7 +49164,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T951" t="inlineStr">
+      <c r="S951" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49246,7 +49216,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T952" t="inlineStr">
+      <c r="S952" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49298,7 +49268,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T953" t="inlineStr">
+      <c r="S953" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49350,7 +49320,7 @@
           <t>lorenzo_sabatino</t>
         </is>
       </c>
-      <c r="T954" t="inlineStr">
+      <c r="S954" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49397,7 +49367,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T955" t="inlineStr">
+      <c r="S955" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49444,7 +49414,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T956" t="inlineStr">
+      <c r="S956" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49496,7 +49466,7 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="T957" t="inlineStr">
+      <c r="S957" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49558,7 +49528,7 @@
           <t>Titolo gridato dagli strilloni: via Merulana nominata come riferimento del delitto, non scena dell'azione; ruolo proposto (D-075).</t>
         </is>
       </c>
-      <c r="T958" t="inlineStr">
+      <c r="S958" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49625,7 +49595,7 @@
           <t>Ancore ai toponimi riconoscibili più prossimi, secondo Terzoli 2015, p. 776: «nei pressi delle Frattocchie […] proprio su un bivio tra l'Appia Antica e la strada per il santuario del Divino Amore, è registrata un'"Osteria"». gaz_via_appia è la via Appia, senza distinzione fra Antica e Nuova (D-087).</t>
         </is>
       </c>
-      <c r="T959" t="inlineStr">
+      <c r="S959" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49682,7 +49652,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T960" t="inlineStr">
+      <c r="S960" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49739,7 +49709,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T961" t="inlineStr">
+      <c r="S961" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49801,17 +49771,17 @@
           <t>La sala di consultazione (la cantina) «dava adito», per uscio con catenaccio, al sacello (QPa 165): vani contigui (D-091).</t>
         </is>
       </c>
+      <c r="Q962" t="inlineStr">
+        <is>
+          <t>cantina_zamira</t>
+        </is>
+      </c>
       <c r="R962" t="inlineStr">
         <is>
-          <t>cantina_zamira</t>
+          <t>adjacentto</t>
         </is>
       </c>
       <c r="S962" t="inlineStr">
-        <is>
-          <t>adjacentto</t>
-        </is>
-      </c>
-      <c r="T962" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49868,7 +49838,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T963" t="inlineStr">
+      <c r="S963" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49930,17 +49900,17 @@
           <t>La Zamira manda a «levarseli in cantina» e a portare i pantaloni «su […] in laboratorio» (QPa 169): la cantina sta sotto il laboratorio (D-091).</t>
         </is>
       </c>
+      <c r="Q964" t="inlineStr">
+        <is>
+          <t>laboratorio_zamira</t>
+        </is>
+      </c>
       <c r="R964" t="inlineStr">
         <is>
-          <t>laboratorio_zamira</t>
+          <t>below</t>
         </is>
       </c>
       <c r="S964" t="inlineStr">
-        <is>
-          <t>below</t>
-        </is>
-      </c>
-      <c r="T964" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -49997,7 +49967,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T965" t="inlineStr">
+      <c r="S965" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -50054,7 +50024,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T966" t="inlineStr">
+      <c r="S966" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -50111,7 +50081,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T967" t="inlineStr">
+      <c r="S967" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -50168,7 +50138,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T968" t="inlineStr">
+      <c r="S968" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -50230,7 +50200,7 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T969" t="inlineStr">
+      <c r="S969" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -50292,22 +50262,22 @@
           <t>Possibile suggestione della via delle Oche di Bologna, nota per le case chiuse: lettura dell'autore, che non incide su statuto e collocazione.</t>
         </is>
       </c>
-      <c r="T970" t="inlineStr">
-        <is>
-          <t>si</t>
+      <c r="S970" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U970" t="inlineStr">
+        <is>
+          <t>interp_00029</t>
         </is>
       </c>
       <c r="V970" t="inlineStr">
         <is>
-          <t>interp_00029</t>
-        </is>
-      </c>
-      <c r="W970" t="inlineStr">
-        <is>
           <t>terzoli_2015</t>
         </is>
       </c>
-      <c r="X970" t="n">
+      <c r="W970" t="n">
         <v>77</v>
       </c>
     </row>
@@ -50367,12 +50337,12 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T971" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="V971" t="inlineStr">
+      <c r="S971" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U971" t="inlineStr">
         <is>
           <t>interp_00552</t>
         </is>
@@ -50434,12 +50404,12 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T972" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="V972" t="inlineStr">
+      <c r="S972" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U972" t="inlineStr">
         <is>
           <t>interp_00553</t>
         </is>
@@ -50501,14 +50471,138 @@
           <t>close_reading</t>
         </is>
       </c>
-      <c r="T973" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
-      <c r="V973" t="inlineStr">
+      <c r="S973" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="U973" t="inlineStr">
         <is>
           <t>interp_00836</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>interp_00983</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>ref_00144</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>dosso_faiti</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>gaz_dosso_faiti</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>projectedspace</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="M974" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N974" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="O974" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="P974" t="inlineStr">
+        <is>
+          <t>Luogo attribuito anche al narratore: la critica vi riconosce una memoria autobiografica dell'autore, il lutto per il fratello Enrico, che affiora attraverso Ingravallo (Perosa 2023a, pp. 103–104; Cortellessa 2023, p. 669; cfr. Lugnani in Perosa 2023a, p. 104, n. 97). Discussione nella tesi, cap. 4 e § 6.4.</t>
+        </is>
+      </c>
+      <c r="S974" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>interp_00984</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>ref_00145</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>monte_cengio</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>gaz_monte_cengio</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>narrator</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>projectedspace</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="M975" t="inlineStr">
+        <is>
+          <t>lorenzo_sabatino</t>
+        </is>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="O975" t="inlineStr">
+        <is>
+          <t>close_reading</t>
+        </is>
+      </c>
+      <c r="P975" t="inlineStr">
+        <is>
+          <t>Luogo attribuito anche al narratore: la critica vi riconosce una memoria autobiografica dell'autore, il lutto per il fratello Enrico, che affiora attraverso Ingravallo (Perosa 2023a, pp. 103–104; Cortellessa 2023, p. 669; cfr. Lugnani in Perosa 2023a, p. 104, n. 97). Discussione nella tesi, cap. 4 e § 6.4.</t>
+        </is>
+      </c>
+      <c r="S975" t="inlineStr">
+        <is>
+          <t>si</t>
         </is>
       </c>
     </row>
